--- a/data/food_loc_exact.xlsx
+++ b/data/food_loc_exact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\food_proj\food_recommendations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5080B13B-73D3-420D-A2F4-C59C874392BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D5362C-0D4E-49C2-8A79-D2ACCBA21057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6226,10 +6226,10 @@
         <v>340</v>
       </c>
       <c r="N85">
-        <v>41.164246200000001</v>
+        <v>34.062860299999997</v>
       </c>
       <c r="O85">
-        <v>-131.1751821</v>
+        <v>-118.14672179999999</v>
       </c>
       <c r="P85" t="s">
         <v>25</v>
@@ -6273,10 +6273,10 @@
         <v>344</v>
       </c>
       <c r="N86">
-        <v>41.199832800000003</v>
+        <v>34.056002599999999</v>
       </c>
       <c r="O86">
-        <v>-131.3281144</v>
+        <v>-118.3124909</v>
       </c>
       <c r="P86" t="s">
         <v>25</v>
@@ -7887,20 +7887,14 @@
       <c r="H121" t="s">
         <v>467</v>
       </c>
-      <c r="K121">
-        <v>41.890756000000003</v>
-      </c>
-      <c r="L121">
-        <v>-87.568399999999997</v>
-      </c>
       <c r="M121" t="s">
         <v>468</v>
       </c>
       <c r="N121">
-        <v>2.8059172000000001</v>
+        <v>41.7038206</v>
       </c>
       <c r="O121">
-        <v>-88.648234799999997</v>
+        <v>-87.801495299999999</v>
       </c>
       <c r="P121" t="s">
         <v>25</v>
@@ -8176,10 +8170,10 @@
         <v>487</v>
       </c>
       <c r="N127">
-        <v>27.5036454</v>
+        <v>41.869528199999998</v>
       </c>
       <c r="O127">
-        <v>-5.2107796999999998</v>
+        <v>-87.665284</v>
       </c>
       <c r="P127" t="s">
         <v>25</v>

--- a/data/food_loc_exact.xlsx
+++ b/data/food_loc_exact.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\food_proj\food_recommendations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D5362C-0D4E-49C2-8A79-D2ACCBA21057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB37045-A97F-4C6A-A567-11C73A889744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="642">
   <si>
     <t>ID</t>
   </si>
@@ -284,18 +284,6 @@
   </si>
   <si>
     <t>https://www.google.com/maps/search/Spin+%26+Savor+Washington,+DC+%2F+Northern+Virginia+area/@40.9620767,-79.9198614,7z/data=!3m1!4b1?entry=ttu&amp;g_ep=EgoyMDI2MTAyMC4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
-    <t>Lubber Run Community Center</t>
-  </si>
-  <si>
-    <t>Community center</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/?api=1&amp;query=Lubber+Run+Community+Center+Washington%2C+DC+%2F+Northern+Virginia+area</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/Lubber+Run+Community+Center+Washington,+DC+%2F+Northern+Virginia+area/@38.8733902,-77.1166358,17z/data=!3m1!4b1?entry=ttu&amp;g_ep=EgoyMDI2MTAyMC4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
   <si>
     <t>Supreme Hot Pot</t>
@@ -2297,7 +2285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q171"/>
+  <dimension ref="A1:Q169"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -2946,10 +2934,10 @@
         <v>82</v>
       </c>
       <c r="N14">
-        <v>40.980814299999999</v>
+        <v>43.087671499999999</v>
       </c>
       <c r="O14">
-        <v>-77.152432000000005</v>
+        <v>-77.614483399999997</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -2993,10 +2981,10 @@
         <v>87</v>
       </c>
       <c r="N15">
-        <v>40.962076699999997</v>
+        <v>43.112105300000003</v>
       </c>
       <c r="O15">
-        <v>-79.919861400000002</v>
+        <v>-77.553055700000002</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -3007,7 +2995,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>88</v>
@@ -3015,35 +3003,38 @@
       <c r="C16" t="s">
         <v>89</v>
       </c>
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
       <c r="E16" t="s">
         <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K16">
-        <v>38.873435999999998</v>
+        <v>38.838161999999997</v>
       </c>
       <c r="L16">
-        <v>-77.114373000000001</v>
+        <v>-77.086487000000005</v>
       </c>
       <c r="M16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N16">
-        <v>38.873390200000003</v>
+        <v>38.864152300000001</v>
       </c>
       <c r="O16">
-        <v>-77.116635799999997</v>
+        <v>-77.083308799999998</v>
       </c>
       <c r="P16" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q16" t="s">
         <v>26</v>
@@ -3051,16 +3042,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
@@ -3069,25 +3060,25 @@
         <v>21</v>
       </c>
       <c r="G17" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" t="s">
+        <v>94</v>
+      </c>
+      <c r="K17">
+        <v>38.885525999999999</v>
+      </c>
+      <c r="L17">
+        <v>-77.059369000000004</v>
+      </c>
+      <c r="M17" t="s">
         <v>95</v>
       </c>
-      <c r="H17" t="s">
-        <v>95</v>
-      </c>
-      <c r="K17">
-        <v>38.838161999999997</v>
-      </c>
-      <c r="L17">
-        <v>-77.086487000000005</v>
-      </c>
-      <c r="M17" t="s">
-        <v>96</v>
-      </c>
       <c r="N17">
-        <v>38.864152300000001</v>
+        <v>38.863822300000002</v>
       </c>
       <c r="O17">
-        <v>-77.083308799999998</v>
+        <v>-77.084786399999999</v>
       </c>
       <c r="P17" t="s">
         <v>32</v>
@@ -3098,16 +3089,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
         <v>97</v>
       </c>
-      <c r="C18" t="s">
-        <v>18</v>
-      </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
         <v>64</v>
@@ -3122,22 +3113,22 @@
         <v>98</v>
       </c>
       <c r="K18">
-        <v>38.885525999999999</v>
+        <v>38.869038000000003</v>
       </c>
       <c r="L18">
-        <v>-77.059369000000004</v>
+        <v>-77.080166000000006</v>
       </c>
       <c r="M18" t="s">
         <v>99</v>
       </c>
       <c r="N18">
-        <v>38.863822300000002</v>
+        <v>38.8643018</v>
       </c>
       <c r="O18">
-        <v>-77.084786399999999</v>
+        <v>-77.170424999999994</v>
       </c>
       <c r="P18" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q18" t="s">
         <v>26</v>
@@ -3145,7 +3136,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
         <v>100</v>
@@ -3169,22 +3160,22 @@
         <v>102</v>
       </c>
       <c r="K19">
-        <v>38.869038000000003</v>
+        <v>38.927700999999999</v>
       </c>
       <c r="L19">
-        <v>-77.080166000000006</v>
+        <v>-77.090888000000007</v>
       </c>
       <c r="M19" t="s">
         <v>103</v>
       </c>
       <c r="N19">
-        <v>38.8643018</v>
+        <v>38.902407400000001</v>
       </c>
       <c r="O19">
-        <v>-77.170424999999994</v>
+        <v>-77.203821500000004</v>
       </c>
       <c r="P19" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q19" t="s">
         <v>26</v>
@@ -3192,13 +3183,13 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
         <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
         <v>54</v>
@@ -3210,28 +3201,28 @@
         <v>21</v>
       </c>
       <c r="G20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" t="s">
+        <v>105</v>
+      </c>
+      <c r="K20">
+        <v>38.926741</v>
+      </c>
+      <c r="L20">
+        <v>-77.114524000000003</v>
+      </c>
+      <c r="M20" t="s">
         <v>106</v>
       </c>
-      <c r="H20" t="s">
-        <v>106</v>
-      </c>
-      <c r="K20">
-        <v>38.927700999999999</v>
-      </c>
-      <c r="L20">
-        <v>-77.090888000000007</v>
-      </c>
-      <c r="M20" t="s">
-        <v>107</v>
-      </c>
       <c r="N20">
-        <v>38.902407400000001</v>
+        <v>38.961098800000002</v>
       </c>
       <c r="O20">
-        <v>-77.203821500000004</v>
+        <v>-77.4832289</v>
       </c>
       <c r="P20" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q20" t="s">
         <v>26</v>
@@ -3239,16 +3230,13 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
         <v>108</v>
-      </c>
-      <c r="C21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" t="s">
-        <v>54</v>
       </c>
       <c r="E21" t="s">
         <v>64</v>
@@ -3263,19 +3251,19 @@
         <v>109</v>
       </c>
       <c r="K21">
-        <v>38.926741</v>
+        <v>38.811239999999998</v>
       </c>
       <c r="L21">
-        <v>-77.114524000000003</v>
+        <v>-77.155400999999998</v>
       </c>
       <c r="M21" t="s">
         <v>110</v>
       </c>
       <c r="N21">
-        <v>37.353985299999998</v>
+        <v>38.891522000000002</v>
       </c>
       <c r="O21">
-        <v>-80.035047899999995</v>
+        <v>-77.064962199999997</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -3286,7 +3274,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
         <v>111</v>
@@ -3294,6 +3282,9 @@
       <c r="C22" t="s">
         <v>112</v>
       </c>
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
       <c r="E22" t="s">
         <v>64</v>
       </c>
@@ -3307,22 +3298,22 @@
         <v>113</v>
       </c>
       <c r="K22">
-        <v>38.811239999999998</v>
+        <v>38.89658</v>
       </c>
       <c r="L22">
-        <v>-77.155400999999998</v>
+        <v>-77.090440000000001</v>
       </c>
       <c r="M22" t="s">
         <v>114</v>
       </c>
       <c r="N22">
-        <v>38.891522000000002</v>
+        <v>38.903477199999998</v>
       </c>
       <c r="O22">
-        <v>-77.064962199999997</v>
+        <v>-77.034975500000002</v>
       </c>
       <c r="P22" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q22" t="s">
         <v>26</v>
@@ -3330,7 +3321,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
         <v>115</v>
@@ -3339,7 +3330,7 @@
         <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="E23" t="s">
         <v>64</v>
@@ -3348,28 +3339,28 @@
         <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K23">
-        <v>38.89658</v>
+        <v>38.944104000000003</v>
       </c>
       <c r="L23">
-        <v>-77.090440000000001</v>
+        <v>-77.182370000000006</v>
       </c>
       <c r="M23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N23">
-        <v>38.903477199999998</v>
+        <v>38.912802200000002</v>
       </c>
       <c r="O23">
-        <v>-77.034975500000002</v>
+        <v>-77.059843200000003</v>
       </c>
       <c r="P23" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q23" t="s">
         <v>26</v>
@@ -3377,16 +3368,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s">
         <v>64</v>
@@ -3395,28 +3386,28 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" t="s">
+        <v>121</v>
+      </c>
+      <c r="K24">
+        <v>38.850009999999997</v>
+      </c>
+      <c r="L24">
+        <v>-77.097367000000006</v>
+      </c>
+      <c r="M24" t="s">
         <v>122</v>
       </c>
-      <c r="H24" t="s">
-        <v>122</v>
-      </c>
-      <c r="K24">
-        <v>38.944104000000003</v>
-      </c>
-      <c r="L24">
-        <v>-77.182370000000006</v>
-      </c>
-      <c r="M24" t="s">
-        <v>123</v>
-      </c>
       <c r="N24">
-        <v>38.912802200000002</v>
+        <v>38.895758000000001</v>
       </c>
       <c r="O24">
-        <v>-77.059843200000003</v>
+        <v>-77.096993999999995</v>
       </c>
       <c r="P24" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q24" t="s">
         <v>26</v>
@@ -3424,43 +3415,40 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
         <v>64</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G25" t="s">
+        <v>124</v>
+      </c>
+      <c r="H25" t="s">
+        <v>124</v>
+      </c>
+      <c r="K25">
+        <v>38.882793999999997</v>
+      </c>
+      <c r="L25">
+        <v>-77.021377000000001</v>
+      </c>
+      <c r="M25" t="s">
         <v>125</v>
       </c>
-      <c r="H25" t="s">
-        <v>125</v>
-      </c>
-      <c r="K25">
-        <v>38.850009999999997</v>
-      </c>
-      <c r="L25">
-        <v>-77.097367000000006</v>
-      </c>
-      <c r="M25" t="s">
-        <v>126</v>
-      </c>
       <c r="N25">
-        <v>38.895758000000001</v>
+        <v>38.883887299999998</v>
       </c>
       <c r="O25">
-        <v>-77.096993999999995</v>
+        <v>-77.025006000000005</v>
       </c>
       <c r="P25" t="s">
         <v>32</v>
@@ -3471,10 +3459,10 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
         <v>68</v>
@@ -3483,28 +3471,28 @@
         <v>64</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H26" t="s">
+        <v>127</v>
+      </c>
+      <c r="K26">
+        <v>38.944113000000002</v>
+      </c>
+      <c r="L26">
+        <v>-77.069704000000002</v>
+      </c>
+      <c r="M26" t="s">
         <v>128</v>
       </c>
-      <c r="H26" t="s">
-        <v>128</v>
-      </c>
-      <c r="K26">
-        <v>38.882793999999997</v>
-      </c>
-      <c r="L26">
-        <v>-77.021377000000001</v>
-      </c>
-      <c r="M26" t="s">
-        <v>129</v>
-      </c>
       <c r="N26">
-        <v>38.883887299999998</v>
+        <v>39.036494400000002</v>
       </c>
       <c r="O26">
-        <v>-77.025006000000005</v>
+        <v>-77.408195300000003</v>
       </c>
       <c r="P26" t="s">
         <v>32</v>
@@ -3515,13 +3503,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>28</v>
+      </c>
+      <c r="D27" t="s">
+        <v>54</v>
       </c>
       <c r="E27" t="s">
         <v>64</v>
@@ -3530,25 +3521,25 @@
         <v>21</v>
       </c>
       <c r="G27" t="s">
+        <v>130</v>
+      </c>
+      <c r="H27" t="s">
+        <v>130</v>
+      </c>
+      <c r="K27">
+        <v>38.899138000000001</v>
+      </c>
+      <c r="L27">
+        <v>-77.238749999999996</v>
+      </c>
+      <c r="M27" t="s">
         <v>131</v>
       </c>
-      <c r="H27" t="s">
-        <v>131</v>
-      </c>
-      <c r="K27">
-        <v>38.944113000000002</v>
-      </c>
-      <c r="L27">
-        <v>-77.069704000000002</v>
-      </c>
-      <c r="M27" t="s">
-        <v>132</v>
-      </c>
       <c r="N27">
-        <v>39.036494400000002</v>
+        <v>38.8473434</v>
       </c>
       <c r="O27">
-        <v>-77.408195300000003</v>
+        <v>-77.303167099999996</v>
       </c>
       <c r="P27" t="s">
         <v>32</v>
@@ -3559,16 +3550,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
         <v>133</v>
       </c>
-      <c r="C28" t="s">
-        <v>28</v>
-      </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s">
         <v>64</v>
@@ -3583,19 +3574,19 @@
         <v>134</v>
       </c>
       <c r="K28">
-        <v>38.899138000000001</v>
+        <v>38.899456999999998</v>
       </c>
       <c r="L28">
-        <v>-77.238749999999996</v>
+        <v>-77.186432999999994</v>
       </c>
       <c r="M28" t="s">
         <v>135</v>
       </c>
       <c r="N28">
-        <v>38.8473434</v>
+        <v>38.886935299999998</v>
       </c>
       <c r="O28">
-        <v>-77.303167099999996</v>
+        <v>-77.177232200000006</v>
       </c>
       <c r="P28" t="s">
         <v>32</v>
@@ -3606,16 +3597,13 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
         <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
-      </c>
-      <c r="D29" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
         <v>64</v>
@@ -3624,25 +3612,25 @@
         <v>21</v>
       </c>
       <c r="G29" t="s">
+        <v>137</v>
+      </c>
+      <c r="H29" t="s">
+        <v>137</v>
+      </c>
+      <c r="K29">
+        <v>38.880001</v>
+      </c>
+      <c r="L29">
+        <v>-77.039246000000006</v>
+      </c>
+      <c r="M29" t="s">
         <v>138</v>
       </c>
-      <c r="H29" t="s">
-        <v>138</v>
-      </c>
-      <c r="K29">
-        <v>38.899456999999998</v>
-      </c>
-      <c r="L29">
-        <v>-77.186432999999994</v>
-      </c>
-      <c r="M29" t="s">
-        <v>139</v>
-      </c>
       <c r="N29">
-        <v>38.886935299999998</v>
+        <v>38.830947999999999</v>
       </c>
       <c r="O29">
-        <v>-77.177232200000006</v>
+        <v>-77.197726000000003</v>
       </c>
       <c r="P29" t="s">
         <v>32</v>
@@ -3653,13 +3641,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>28</v>
+      </c>
+      <c r="D30" t="s">
+        <v>54</v>
       </c>
       <c r="E30" t="s">
         <v>64</v>
@@ -3668,25 +3659,25 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
+        <v>140</v>
+      </c>
+      <c r="H30" t="s">
+        <v>140</v>
+      </c>
+      <c r="K30">
+        <v>38.889845999999999</v>
+      </c>
+      <c r="L30">
+        <v>-77.066596000000004</v>
+      </c>
+      <c r="M30" t="s">
         <v>141</v>
       </c>
-      <c r="H30" t="s">
-        <v>141</v>
-      </c>
-      <c r="K30">
-        <v>38.880001</v>
-      </c>
-      <c r="L30">
-        <v>-77.039246000000006</v>
-      </c>
-      <c r="M30" t="s">
-        <v>142</v>
-      </c>
       <c r="N30">
-        <v>38.830947999999999</v>
+        <v>38.852856500000001</v>
       </c>
       <c r="O30">
-        <v>-77.197726000000003</v>
+        <v>-77.134799200000003</v>
       </c>
       <c r="P30" t="s">
         <v>32</v>
@@ -3697,16 +3688,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
         <v>64</v>
@@ -3715,28 +3706,28 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
+        <v>143</v>
+      </c>
+      <c r="H31" t="s">
+        <v>143</v>
+      </c>
+      <c r="K31">
+        <v>38.928663999999998</v>
+      </c>
+      <c r="L31">
+        <v>-77.146908999999994</v>
+      </c>
+      <c r="M31" t="s">
         <v>144</v>
       </c>
-      <c r="H31" t="s">
-        <v>144</v>
-      </c>
-      <c r="K31">
-        <v>38.889845999999999</v>
-      </c>
-      <c r="L31">
-        <v>-77.066596000000004</v>
-      </c>
-      <c r="M31" t="s">
-        <v>145</v>
-      </c>
       <c r="N31">
-        <v>38.852856500000001</v>
+        <v>38.884422700000002</v>
       </c>
       <c r="O31">
-        <v>-77.134799200000003</v>
+        <v>-77.381485699999999</v>
       </c>
       <c r="P31" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q31" t="s">
         <v>26</v>
@@ -3744,16 +3735,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" t="s">
         <v>146</v>
       </c>
-      <c r="C32" t="s">
-        <v>18</v>
-      </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="E32" t="s">
         <v>64</v>
@@ -3762,28 +3753,28 @@
         <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K32">
-        <v>38.928663999999998</v>
+        <v>38.846555000000002</v>
       </c>
       <c r="L32">
-        <v>-77.146908999999994</v>
+        <v>-77.077613999999997</v>
       </c>
       <c r="M32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N32">
-        <v>38.884422700000002</v>
+        <v>38.890933599999997</v>
       </c>
       <c r="O32">
-        <v>-77.381485699999999</v>
+        <v>-77.184186299999993</v>
       </c>
       <c r="P32" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q32" t="s">
         <v>26</v>
@@ -3791,16 +3782,13 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
-      </c>
-      <c r="D33" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="E33" t="s">
         <v>64</v>
@@ -3809,28 +3797,28 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
+        <v>151</v>
+      </c>
+      <c r="H33" t="s">
+        <v>151</v>
+      </c>
+      <c r="K33">
+        <v>38.905197000000001</v>
+      </c>
+      <c r="L33">
+        <v>-77.064964000000003</v>
+      </c>
+      <c r="M33" t="s">
         <v>152</v>
       </c>
-      <c r="H33" t="s">
-        <v>152</v>
-      </c>
-      <c r="K33">
-        <v>38.846555000000002</v>
-      </c>
-      <c r="L33">
-        <v>-77.077613999999997</v>
-      </c>
-      <c r="M33" t="s">
-        <v>153</v>
-      </c>
       <c r="N33">
-        <v>38.890933599999997</v>
+        <v>38.900332300000002</v>
       </c>
       <c r="O33">
-        <v>-77.184186299999993</v>
+        <v>-77.326886900000005</v>
       </c>
       <c r="P33" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q33" t="s">
         <v>26</v>
@@ -3838,13 +3826,16 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>28</v>
+      </c>
+      <c r="D34" t="s">
+        <v>54</v>
       </c>
       <c r="E34" t="s">
         <v>64</v>
@@ -3853,28 +3844,28 @@
         <v>21</v>
       </c>
       <c r="G34" t="s">
+        <v>154</v>
+      </c>
+      <c r="H34" t="s">
+        <v>154</v>
+      </c>
+      <c r="K34">
+        <v>38.930321999999997</v>
+      </c>
+      <c r="L34">
+        <v>-77.035296000000002</v>
+      </c>
+      <c r="M34" t="s">
         <v>155</v>
       </c>
-      <c r="H34" t="s">
-        <v>155</v>
-      </c>
-      <c r="K34">
-        <v>38.905197000000001</v>
-      </c>
-      <c r="L34">
-        <v>-77.064964000000003</v>
-      </c>
-      <c r="M34" t="s">
-        <v>156</v>
-      </c>
       <c r="N34">
-        <v>38.900332300000002</v>
+        <v>38.853106099999998</v>
       </c>
       <c r="O34">
-        <v>-77.326886900000005</v>
+        <v>-77.340435299999996</v>
       </c>
       <c r="P34" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q34" t="s">
         <v>26</v>
@@ -3882,16 +3873,13 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" t="s">
         <v>157</v>
-      </c>
-      <c r="C35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" t="s">
-        <v>54</v>
       </c>
       <c r="E35" t="s">
         <v>64</v>
@@ -3906,19 +3894,19 @@
         <v>158</v>
       </c>
       <c r="K35">
-        <v>38.930321999999997</v>
+        <v>38.843761999999998</v>
       </c>
       <c r="L35">
-        <v>-77.035296000000002</v>
+        <v>-77.047859000000003</v>
       </c>
       <c r="M35" t="s">
         <v>159</v>
       </c>
       <c r="N35">
-        <v>38.853106099999998</v>
+        <v>38.881181400000003</v>
       </c>
       <c r="O35">
-        <v>-77.340435299999996</v>
+        <v>-77.027962299999999</v>
       </c>
       <c r="P35" t="s">
         <v>32</v>
@@ -3929,13 +3917,16 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
         <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>161</v>
+        <v>77</v>
+      </c>
+      <c r="D36" t="s">
+        <v>147</v>
       </c>
       <c r="E36" t="s">
         <v>64</v>
@@ -3944,25 +3935,25 @@
         <v>21</v>
       </c>
       <c r="G36" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" t="s">
+        <v>161</v>
+      </c>
+      <c r="K36">
+        <v>38.910677</v>
+      </c>
+      <c r="L36">
+        <v>-76.941664000000003</v>
+      </c>
+      <c r="M36" t="s">
         <v>162</v>
       </c>
-      <c r="H36" t="s">
-        <v>162</v>
-      </c>
-      <c r="K36">
-        <v>38.843761999999998</v>
-      </c>
-      <c r="L36">
-        <v>-77.047859000000003</v>
-      </c>
-      <c r="M36" t="s">
-        <v>163</v>
-      </c>
       <c r="N36">
-        <v>38.881181400000003</v>
+        <v>39.063162699999999</v>
       </c>
       <c r="O36">
-        <v>-77.027962299999999</v>
+        <v>-77.124311800000001</v>
       </c>
       <c r="P36" t="s">
         <v>32</v>
@@ -3973,22 +3964,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" t="s">
         <v>164</v>
-      </c>
-      <c r="C37" t="s">
-        <v>77</v>
-      </c>
-      <c r="D37" t="s">
-        <v>151</v>
       </c>
       <c r="E37" t="s">
         <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G37" t="s">
         <v>165</v>
@@ -3997,22 +3988,22 @@
         <v>165</v>
       </c>
       <c r="K37">
-        <v>38.910677</v>
+        <v>41.879365</v>
       </c>
       <c r="L37">
-        <v>-76.941664000000003</v>
+        <v>-87.626452</v>
       </c>
       <c r="M37" t="s">
         <v>166</v>
       </c>
       <c r="N37">
-        <v>39.063162699999999</v>
+        <v>38.896536900000001</v>
       </c>
       <c r="O37">
-        <v>-77.124311800000001</v>
+        <v>-77.085654899999994</v>
       </c>
       <c r="P37" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q37" t="s">
         <v>26</v>
@@ -4020,22 +4011,22 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
         <v>167</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="D38" t="s">
-        <v>168</v>
+        <v>45</v>
       </c>
       <c r="E38" t="s">
         <v>64</v>
       </c>
       <c r="F38" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G38" t="s">
         <v>169</v>
@@ -4044,22 +4035,22 @@
         <v>169</v>
       </c>
       <c r="K38">
-        <v>41.879365</v>
+        <v>38.874892000000003</v>
       </c>
       <c r="L38">
-        <v>-87.626452</v>
+        <v>-77.105399000000006</v>
       </c>
       <c r="M38" t="s">
         <v>170</v>
       </c>
       <c r="N38">
-        <v>38.896536900000001</v>
+        <v>38.890194100000002</v>
       </c>
       <c r="O38">
-        <v>-77.085654899999994</v>
+        <v>-77.086535400000002</v>
       </c>
       <c r="P38" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q38" t="s">
         <v>26</v>
@@ -4067,7 +4058,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
         <v>171</v>
@@ -4076,7 +4067,7 @@
         <v>172</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="E39" t="s">
         <v>64</v>
@@ -4085,25 +4076,25 @@
         <v>21</v>
       </c>
       <c r="G39" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H39" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K39">
-        <v>38.874892000000003</v>
+        <v>38.929597000000001</v>
       </c>
       <c r="L39">
-        <v>-77.105399000000006</v>
+        <v>-77.013104999999996</v>
       </c>
       <c r="M39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N39">
-        <v>38.890194100000002</v>
+        <v>38.897542700000002</v>
       </c>
       <c r="O39">
-        <v>-77.086535400000002</v>
+        <v>-77.443059399999996</v>
       </c>
       <c r="P39" t="s">
         <v>32</v>
@@ -4114,15 +4105,12 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C40" t="s">
-        <v>176</v>
-      </c>
-      <c r="D40" t="s">
         <v>177</v>
       </c>
       <c r="E40" t="s">
@@ -4138,19 +4126,19 @@
         <v>178</v>
       </c>
       <c r="K40">
-        <v>38.929597000000001</v>
+        <v>38.867387000000001</v>
       </c>
       <c r="L40">
-        <v>-77.013104999999996</v>
+        <v>-77.116274000000004</v>
       </c>
       <c r="M40" t="s">
         <v>179</v>
       </c>
       <c r="N40">
-        <v>38.897542700000002</v>
+        <v>38.818825099999998</v>
       </c>
       <c r="O40">
-        <v>-77.443059399999996</v>
+        <v>-77.142314600000006</v>
       </c>
       <c r="P40" t="s">
         <v>32</v>
@@ -4161,7 +4149,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
         <v>180</v>
@@ -4169,32 +4157,35 @@
       <c r="C41" t="s">
         <v>181</v>
       </c>
+      <c r="D41" t="s">
+        <v>45</v>
+      </c>
       <c r="E41" t="s">
-        <v>64</v>
+        <v>182</v>
       </c>
       <c r="F41" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K41">
-        <v>38.867387000000001</v>
+        <v>49.250473</v>
       </c>
       <c r="L41">
-        <v>-77.116274000000004</v>
+        <v>-123.046001</v>
       </c>
       <c r="M41" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N41">
-        <v>38.818825099999998</v>
+        <v>49.2440943</v>
       </c>
       <c r="O41">
-        <v>-77.142314600000006</v>
+        <v>-123.0624803</v>
       </c>
       <c r="P41" t="s">
         <v>32</v>
@@ -4205,43 +4196,43 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>89</v>
       </c>
       <c r="D42" t="s">
         <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F42" t="s">
         <v>55</v>
       </c>
       <c r="G42" t="s">
+        <v>186</v>
+      </c>
+      <c r="H42" t="s">
+        <v>186</v>
+      </c>
+      <c r="K42">
+        <v>49.236820000000002</v>
+      </c>
+      <c r="L42">
+        <v>-123.064621</v>
+      </c>
+      <c r="M42" t="s">
         <v>187</v>
       </c>
-      <c r="H42" t="s">
-        <v>187</v>
-      </c>
-      <c r="K42">
-        <v>49.250473</v>
-      </c>
-      <c r="L42">
-        <v>-123.046001</v>
-      </c>
-      <c r="M42" t="s">
-        <v>188</v>
-      </c>
       <c r="N42">
-        <v>49.2440943</v>
+        <v>49.244220900000002</v>
       </c>
       <c r="O42">
-        <v>-123.0624803</v>
+        <v>-123.0627874</v>
       </c>
       <c r="P42" t="s">
         <v>32</v>
@@ -4252,22 +4243,22 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
+        <v>188</v>
+      </c>
+      <c r="C43" t="s">
         <v>189</v>
       </c>
-      <c r="C43" t="s">
-        <v>93</v>
-      </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G43" t="s">
         <v>190</v>
@@ -4276,19 +4267,19 @@
         <v>190</v>
       </c>
       <c r="K43">
-        <v>49.236820000000002</v>
+        <v>49.158493</v>
       </c>
       <c r="L43">
-        <v>-123.064621</v>
+        <v>-123.095838</v>
       </c>
       <c r="M43" t="s">
         <v>191</v>
       </c>
       <c r="N43">
-        <v>49.244220900000002</v>
+        <v>49.183245800000002</v>
       </c>
       <c r="O43">
-        <v>-123.0627874</v>
+        <v>-123.1266071</v>
       </c>
       <c r="P43" t="s">
         <v>32</v>
@@ -4299,46 +4290,46 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="D44" t="s">
         <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F44" t="s">
         <v>21</v>
       </c>
       <c r="G44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H44" t="s">
+        <v>193</v>
+      </c>
+      <c r="K44">
+        <v>49.218791000000003</v>
+      </c>
+      <c r="L44">
+        <v>-123.019925</v>
+      </c>
+      <c r="M44" t="s">
         <v>194</v>
       </c>
-      <c r="H44" t="s">
-        <v>194</v>
-      </c>
-      <c r="K44">
-        <v>49.158493</v>
-      </c>
-      <c r="L44">
-        <v>-123.095838</v>
-      </c>
-      <c r="M44" t="s">
-        <v>195</v>
-      </c>
       <c r="N44">
-        <v>49.183245800000002</v>
+        <v>49.311007600000003</v>
       </c>
       <c r="O44">
-        <v>-123.1266071</v>
+        <v>-123.13019490000001</v>
       </c>
       <c r="P44" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q44" t="s">
         <v>26</v>
@@ -4346,19 +4337,19 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" t="s">
         <v>196</v>
       </c>
-      <c r="C45" t="s">
-        <v>28</v>
-      </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F45" t="s">
         <v>21</v>
@@ -4370,22 +4361,22 @@
         <v>197</v>
       </c>
       <c r="K45">
-        <v>49.218791000000003</v>
+        <v>49.207822</v>
       </c>
       <c r="L45">
-        <v>-123.019925</v>
+        <v>-123.260819</v>
       </c>
       <c r="M45" t="s">
         <v>198</v>
       </c>
       <c r="N45">
-        <v>49.311007600000003</v>
+        <v>49.210706399999999</v>
       </c>
       <c r="O45">
-        <v>-123.13019490000001</v>
+        <v>-122.9346498</v>
       </c>
       <c r="P45" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q45" t="s">
         <v>26</v>
@@ -4393,43 +4384,43 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
         <v>199</v>
       </c>
       <c r="C46" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="D46" t="s">
         <v>45</v>
       </c>
       <c r="E46" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F46" t="s">
         <v>21</v>
       </c>
       <c r="G46" t="s">
+        <v>200</v>
+      </c>
+      <c r="H46" t="s">
+        <v>200</v>
+      </c>
+      <c r="K46">
+        <v>49.136750999999997</v>
+      </c>
+      <c r="L46">
+        <v>-123.11017099999999</v>
+      </c>
+      <c r="M46" t="s">
         <v>201</v>
       </c>
-      <c r="H46" t="s">
-        <v>201</v>
-      </c>
-      <c r="K46">
-        <v>49.207822</v>
-      </c>
-      <c r="L46">
-        <v>-123.260819</v>
-      </c>
-      <c r="M46" t="s">
-        <v>202</v>
-      </c>
       <c r="N46">
-        <v>49.210706399999999</v>
+        <v>49.224086300000003</v>
       </c>
       <c r="O46">
-        <v>-122.9346498</v>
+        <v>-122.9416219</v>
       </c>
       <c r="P46" t="s">
         <v>32</v>
@@ -4440,19 +4431,16 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
+        <v>202</v>
+      </c>
+      <c r="C47" t="s">
         <v>203</v>
       </c>
-      <c r="C47" t="s">
-        <v>185</v>
-      </c>
-      <c r="D47" t="s">
-        <v>45</v>
-      </c>
       <c r="E47" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F47" t="s">
         <v>21</v>
@@ -4464,22 +4452,22 @@
         <v>204</v>
       </c>
       <c r="K47">
-        <v>49.136750999999997</v>
+        <v>49.152636000000001</v>
       </c>
       <c r="L47">
-        <v>-123.11017099999999</v>
+        <v>-123.17455099999999</v>
       </c>
       <c r="M47" t="s">
         <v>205</v>
       </c>
       <c r="N47">
-        <v>49.224086300000003</v>
+        <v>49.2709768</v>
       </c>
       <c r="O47">
-        <v>-122.9416219</v>
+        <v>-123.26325</v>
       </c>
       <c r="P47" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q47" t="s">
         <v>26</v>
@@ -4487,7 +4475,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
         <v>206</v>
@@ -4496,7 +4484,7 @@
         <v>207</v>
       </c>
       <c r="E48" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F48" t="s">
         <v>21</v>
@@ -4508,22 +4496,22 @@
         <v>208</v>
       </c>
       <c r="K48">
-        <v>49.152636000000001</v>
+        <v>49.345787000000001</v>
       </c>
       <c r="L48">
-        <v>-123.17455099999999</v>
+        <v>-123.189756</v>
       </c>
       <c r="M48" t="s">
         <v>209</v>
       </c>
       <c r="N48">
-        <v>49.2709768</v>
+        <v>49.2679331</v>
       </c>
       <c r="O48">
-        <v>-123.26325</v>
+        <v>-123.1490012</v>
       </c>
       <c r="P48" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q48" t="s">
         <v>26</v>
@@ -4531,40 +4519,40 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
         <v>210</v>
       </c>
       <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" t="s">
+        <v>182</v>
+      </c>
+      <c r="F49" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" t="s">
         <v>211</v>
       </c>
-      <c r="E49" t="s">
-        <v>186</v>
-      </c>
-      <c r="F49" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
+        <v>211</v>
+      </c>
+      <c r="K49">
+        <v>49.163249999999998</v>
+      </c>
+      <c r="L49">
+        <v>-122.990641</v>
+      </c>
+      <c r="M49" t="s">
         <v>212</v>
       </c>
-      <c r="H49" t="s">
-        <v>212</v>
-      </c>
-      <c r="K49">
-        <v>49.345787000000001</v>
-      </c>
-      <c r="L49">
-        <v>-123.189756</v>
-      </c>
-      <c r="M49" t="s">
-        <v>213</v>
-      </c>
       <c r="N49">
-        <v>49.2679331</v>
+        <v>49.2825676</v>
       </c>
       <c r="O49">
-        <v>-123.1490012</v>
+        <v>-122.9539784</v>
       </c>
       <c r="P49" t="s">
         <v>32</v>
@@ -4575,16 +4563,16 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
+        <v>213</v>
+      </c>
+      <c r="C50" t="s">
         <v>214</v>
       </c>
-      <c r="C50" t="s">
-        <v>68</v>
-      </c>
       <c r="E50" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F50" t="s">
         <v>21</v>
@@ -4596,19 +4584,19 @@
         <v>215</v>
       </c>
       <c r="K50">
-        <v>49.163249999999998</v>
+        <v>49.249423999999998</v>
       </c>
       <c r="L50">
-        <v>-122.990641</v>
+        <v>-122.948121</v>
       </c>
       <c r="M50" t="s">
         <v>216</v>
       </c>
       <c r="N50">
-        <v>49.2825676</v>
+        <v>49.281323</v>
       </c>
       <c r="O50">
-        <v>-122.9539784</v>
+        <v>-122.958251</v>
       </c>
       <c r="P50" t="s">
         <v>32</v>
@@ -4619,43 +4607,43 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
         <v>217</v>
       </c>
       <c r="C51" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" t="s">
         <v>218</v>
       </c>
-      <c r="E51" t="s">
-        <v>186</v>
-      </c>
-      <c r="F51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
+        <v>218</v>
+      </c>
+      <c r="K51">
+        <v>49.222155999999998</v>
+      </c>
+      <c r="L51">
+        <v>-122.91997600000001</v>
+      </c>
+      <c r="M51" t="s">
         <v>219</v>
       </c>
-      <c r="H51" t="s">
-        <v>219</v>
-      </c>
-      <c r="K51">
-        <v>49.249423999999998</v>
-      </c>
-      <c r="L51">
-        <v>-122.948121</v>
-      </c>
-      <c r="M51" t="s">
-        <v>220</v>
-      </c>
       <c r="N51">
-        <v>49.281323</v>
+        <v>49.178742</v>
       </c>
       <c r="O51">
-        <v>-122.958251</v>
+        <v>-123.1985013</v>
       </c>
       <c r="P51" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q51" t="s">
         <v>26</v>
@@ -4663,43 +4651,46 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
+        <v>220</v>
+      </c>
+      <c r="C52" t="s">
         <v>221</v>
       </c>
-      <c r="C52" t="s">
-        <v>112</v>
+      <c r="D52" t="s">
+        <v>222</v>
       </c>
       <c r="E52" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F52" t="s">
         <v>21</v>
       </c>
       <c r="G52" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H52" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K52">
-        <v>49.222155999999998</v>
+        <v>49.213214000000001</v>
       </c>
       <c r="L52">
-        <v>-122.91997600000001</v>
+        <v>-122.909852</v>
       </c>
       <c r="M52" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N52">
-        <v>49.178742</v>
+        <v>41.895955899999997</v>
       </c>
       <c r="O52">
-        <v>-123.1985013</v>
+        <v>-87.634329600000001</v>
       </c>
       <c r="P52" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q52" t="s">
         <v>26</v>
@@ -4707,19 +4698,19 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D53" t="s">
-        <v>226</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F53" t="s">
         <v>21</v>
@@ -4731,19 +4722,19 @@
         <v>227</v>
       </c>
       <c r="K53">
-        <v>49.213214000000001</v>
+        <v>49.199299000000003</v>
       </c>
       <c r="L53">
-        <v>-122.909852</v>
+        <v>-123.104257</v>
       </c>
       <c r="M53" t="s">
         <v>228</v>
       </c>
       <c r="N53">
-        <v>41.895955899999997</v>
+        <v>49.280937000000002</v>
       </c>
       <c r="O53">
-        <v>-87.634329600000001</v>
+        <v>-123.0219022</v>
       </c>
       <c r="P53" t="s">
         <v>32</v>
@@ -4754,43 +4745,43 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
         <v>229</v>
       </c>
       <c r="C54" t="s">
-        <v>230</v>
+        <v>84</v>
       </c>
       <c r="D54" t="s">
         <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F54" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G54" t="s">
+        <v>230</v>
+      </c>
+      <c r="H54" t="s">
+        <v>230</v>
+      </c>
+      <c r="K54">
+        <v>49.254488000000002</v>
+      </c>
+      <c r="L54">
+        <v>-122.90701199999999</v>
+      </c>
+      <c r="M54" t="s">
         <v>231</v>
       </c>
-      <c r="H54" t="s">
-        <v>231</v>
-      </c>
-      <c r="K54">
-        <v>49.199299000000003</v>
-      </c>
-      <c r="L54">
-        <v>-123.104257</v>
-      </c>
-      <c r="M54" t="s">
-        <v>232</v>
-      </c>
       <c r="N54">
-        <v>49.280937000000002</v>
+        <v>49.242746799999999</v>
       </c>
       <c r="O54">
-        <v>-123.0219022</v>
+        <v>-122.89238899999999</v>
       </c>
       <c r="P54" t="s">
         <v>32</v>
@@ -4801,22 +4792,22 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" t="s">
+        <v>232</v>
+      </c>
+      <c r="C55" t="s">
         <v>233</v>
-      </c>
-      <c r="C55" t="s">
-        <v>84</v>
       </c>
       <c r="D55" t="s">
         <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F55" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G55" t="s">
         <v>234</v>
@@ -4825,22 +4816,22 @@
         <v>234</v>
       </c>
       <c r="K55">
-        <v>49.254488000000002</v>
+        <v>49.199883999999997</v>
       </c>
       <c r="L55">
-        <v>-122.90701199999999</v>
+        <v>-123.137261</v>
       </c>
       <c r="M55" t="s">
         <v>235</v>
       </c>
       <c r="N55">
-        <v>49.242746799999999</v>
+        <v>49.250507800000001</v>
       </c>
       <c r="O55">
-        <v>-122.89238899999999</v>
+        <v>-123.11471760000001</v>
       </c>
       <c r="P55" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q55" t="s">
         <v>26</v>
@@ -4848,46 +4839,46 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56" t="s">
         <v>236</v>
       </c>
       <c r="C56" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="D56" t="s">
         <v>45</v>
       </c>
       <c r="E56" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F56" t="s">
         <v>21</v>
       </c>
       <c r="G56" t="s">
+        <v>237</v>
+      </c>
+      <c r="H56" t="s">
+        <v>237</v>
+      </c>
+      <c r="K56">
+        <v>49.318542000000001</v>
+      </c>
+      <c r="L56">
+        <v>-122.97890099999999</v>
+      </c>
+      <c r="M56" t="s">
         <v>238</v>
       </c>
-      <c r="H56" t="s">
-        <v>238</v>
-      </c>
-      <c r="K56">
-        <v>49.199883999999997</v>
-      </c>
-      <c r="L56">
-        <v>-123.137261</v>
-      </c>
-      <c r="M56" t="s">
-        <v>239</v>
-      </c>
       <c r="N56">
-        <v>49.250507800000001</v>
+        <v>49.239213900000003</v>
       </c>
       <c r="O56">
-        <v>-123.11471760000001</v>
+        <v>-123.05282529999999</v>
       </c>
       <c r="P56" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q56" t="s">
         <v>26</v>
@@ -4895,43 +4886,43 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C57" t="s">
-        <v>185</v>
+        <v>89</v>
       </c>
       <c r="D57" t="s">
         <v>45</v>
       </c>
       <c r="E57" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F57" t="s">
         <v>21</v>
       </c>
       <c r="G57" t="s">
+        <v>240</v>
+      </c>
+      <c r="H57" t="s">
+        <v>240</v>
+      </c>
+      <c r="K57">
+        <v>49.205832000000001</v>
+      </c>
+      <c r="L57">
+        <v>-123.005036</v>
+      </c>
+      <c r="M57" t="s">
         <v>241</v>
       </c>
-      <c r="H57" t="s">
-        <v>241</v>
-      </c>
-      <c r="K57">
-        <v>49.318542000000001</v>
-      </c>
-      <c r="L57">
-        <v>-122.97890099999999</v>
-      </c>
-      <c r="M57" t="s">
-        <v>242</v>
-      </c>
       <c r="N57">
-        <v>49.239213900000003</v>
+        <v>49.170463099999999</v>
       </c>
       <c r="O57">
-        <v>-123.05282529999999</v>
+        <v>-123.1330004</v>
       </c>
       <c r="P57" t="s">
         <v>32</v>
@@ -4942,19 +4933,19 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" t="s">
         <v>243</v>
       </c>
-      <c r="C58" t="s">
-        <v>93</v>
-      </c>
       <c r="D58" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E58" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F58" t="s">
         <v>21</v>
@@ -4966,22 +4957,22 @@
         <v>244</v>
       </c>
       <c r="K58">
-        <v>49.205832000000001</v>
+        <v>49.266337</v>
       </c>
       <c r="L58">
-        <v>-123.005036</v>
+        <v>-122.88421700000001</v>
       </c>
       <c r="M58" t="s">
         <v>245</v>
       </c>
       <c r="N58">
-        <v>49.170463099999999</v>
+        <v>49.201298700000002</v>
       </c>
       <c r="O58">
-        <v>-123.1330004</v>
+        <v>-123.1627024</v>
       </c>
       <c r="P58" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q58" t="s">
         <v>26</v>
@@ -4989,22 +4980,22 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
         <v>246</v>
       </c>
       <c r="C59" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" t="s">
         <v>247</v>
       </c>
-      <c r="D59" t="s">
-        <v>54</v>
-      </c>
       <c r="E59" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F59" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G59" t="s">
         <v>248</v>
@@ -5013,22 +5004,22 @@
         <v>248</v>
       </c>
       <c r="K59">
-        <v>49.266337</v>
+        <v>49.274774999999998</v>
       </c>
       <c r="L59">
-        <v>-122.88421700000001</v>
+        <v>-123.119096</v>
       </c>
       <c r="M59" t="s">
         <v>249</v>
       </c>
       <c r="N59">
-        <v>49.201298700000002</v>
+        <v>49.171094799999999</v>
       </c>
       <c r="O59">
-        <v>-123.1627024</v>
+        <v>-123.13604340000001</v>
       </c>
       <c r="P59" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q59" t="s">
         <v>26</v>
@@ -5036,43 +5027,43 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
         <v>250</v>
       </c>
       <c r="C60" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D60" t="s">
+        <v>45</v>
+      </c>
+      <c r="E60" t="s">
+        <v>182</v>
+      </c>
+      <c r="F60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60" t="s">
         <v>251</v>
       </c>
-      <c r="E60" t="s">
-        <v>186</v>
-      </c>
-      <c r="F60" t="s">
-        <v>55</v>
-      </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
+        <v>251</v>
+      </c>
+      <c r="K60">
+        <v>49.303106999999997</v>
+      </c>
+      <c r="L60">
+        <v>-123.00279999999999</v>
+      </c>
+      <c r="M60" t="s">
         <v>252</v>
       </c>
-      <c r="H60" t="s">
-        <v>252</v>
-      </c>
-      <c r="K60">
-        <v>49.274774999999998</v>
-      </c>
-      <c r="L60">
-        <v>-123.119096</v>
-      </c>
-      <c r="M60" t="s">
-        <v>253</v>
-      </c>
       <c r="N60">
-        <v>49.171094799999999</v>
+        <v>49.1841054</v>
       </c>
       <c r="O60">
-        <v>-123.13604340000001</v>
+        <v>-123.1359947</v>
       </c>
       <c r="P60" t="s">
         <v>32</v>
@@ -5083,43 +5074,43 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B61" t="s">
+        <v>253</v>
+      </c>
+      <c r="C61" t="s">
+        <v>133</v>
+      </c>
+      <c r="D61" t="s">
+        <v>54</v>
+      </c>
+      <c r="E61" t="s">
+        <v>182</v>
+      </c>
+      <c r="F61" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" t="s">
         <v>254</v>
       </c>
-      <c r="C61" t="s">
-        <v>84</v>
-      </c>
-      <c r="D61" t="s">
-        <v>45</v>
-      </c>
-      <c r="E61" t="s">
-        <v>186</v>
-      </c>
-      <c r="F61" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
+        <v>254</v>
+      </c>
+      <c r="K61">
+        <v>49.251823000000002</v>
+      </c>
+      <c r="L61">
+        <v>-123.25277</v>
+      </c>
+      <c r="M61" t="s">
         <v>255</v>
       </c>
-      <c r="H61" t="s">
-        <v>255</v>
-      </c>
-      <c r="K61">
-        <v>49.303106999999997</v>
-      </c>
-      <c r="L61">
-        <v>-123.00279999999999</v>
-      </c>
-      <c r="M61" t="s">
-        <v>256</v>
-      </c>
       <c r="N61">
-        <v>49.1841054</v>
+        <v>49.170513100000001</v>
       </c>
       <c r="O61">
-        <v>-123.1359947</v>
+        <v>-123.13269510000001</v>
       </c>
       <c r="P61" t="s">
         <v>32</v>
@@ -5130,22 +5121,22 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
+        <v>256</v>
+      </c>
+      <c r="C62" t="s">
+        <v>84</v>
+      </c>
+      <c r="D62" t="s">
         <v>257</v>
       </c>
-      <c r="C62" t="s">
-        <v>137</v>
-      </c>
-      <c r="D62" t="s">
-        <v>54</v>
-      </c>
       <c r="E62" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F62" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G62" t="s">
         <v>258</v>
@@ -5154,19 +5145,19 @@
         <v>258</v>
       </c>
       <c r="K62">
-        <v>49.251823000000002</v>
+        <v>49.276097</v>
       </c>
       <c r="L62">
-        <v>-123.25277</v>
+        <v>-123.129521</v>
       </c>
       <c r="M62" t="s">
         <v>259</v>
       </c>
       <c r="N62">
-        <v>49.170513100000001</v>
+        <v>49.281391499999998</v>
       </c>
       <c r="O62">
-        <v>-123.13269510000001</v>
+        <v>-123.1336479</v>
       </c>
       <c r="P62" t="s">
         <v>32</v>
@@ -5177,43 +5168,43 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
         <v>260</v>
       </c>
       <c r="C63" t="s">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E63" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F63" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K63">
-        <v>49.276097</v>
+        <v>49.176242999999999</v>
       </c>
       <c r="L63">
-        <v>-123.129521</v>
+        <v>-123.04689999999999</v>
       </c>
       <c r="M63" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N63">
-        <v>49.281391499999998</v>
+        <v>49.170431800000003</v>
       </c>
       <c r="O63">
-        <v>-123.1336479</v>
+        <v>-123.13873959999999</v>
       </c>
       <c r="P63" t="s">
         <v>32</v>
@@ -5224,43 +5215,43 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C64" t="s">
-        <v>265</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" t="s">
+        <v>182</v>
+      </c>
+      <c r="F64" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" t="s">
         <v>266</v>
       </c>
-      <c r="E64" t="s">
-        <v>186</v>
-      </c>
-      <c r="F64" t="s">
-        <v>21</v>
-      </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
+        <v>266</v>
+      </c>
+      <c r="K64">
+        <v>49.209524000000002</v>
+      </c>
+      <c r="L64">
+        <v>-122.976842</v>
+      </c>
+      <c r="M64" t="s">
         <v>267</v>
       </c>
-      <c r="H64" t="s">
-        <v>267</v>
-      </c>
-      <c r="K64">
-        <v>49.176242999999999</v>
-      </c>
-      <c r="L64">
-        <v>-123.04689999999999</v>
-      </c>
-      <c r="M64" t="s">
-        <v>268</v>
-      </c>
       <c r="N64">
-        <v>49.170431800000003</v>
+        <v>49.171042900000003</v>
       </c>
       <c r="O64">
-        <v>-123.13873959999999</v>
+        <v>-123.1398264</v>
       </c>
       <c r="P64" t="s">
         <v>32</v>
@@ -5271,22 +5262,22 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
+        <v>268</v>
+      </c>
+      <c r="C65" t="s">
         <v>269</v>
       </c>
-      <c r="C65" t="s">
-        <v>18</v>
-      </c>
       <c r="D65" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="E65" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F65" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G65" t="s">
         <v>270</v>
@@ -5295,19 +5286,19 @@
         <v>270</v>
       </c>
       <c r="K65">
-        <v>49.209524000000002</v>
+        <v>49.156863000000001</v>
       </c>
       <c r="L65">
-        <v>-122.976842</v>
+        <v>-123.139976</v>
       </c>
       <c r="M65" t="s">
         <v>271</v>
       </c>
       <c r="N65">
-        <v>49.171042900000003</v>
+        <v>49.179198300000003</v>
       </c>
       <c r="O65">
-        <v>-123.1398264</v>
+        <v>-123.1249191</v>
       </c>
       <c r="P65" t="s">
         <v>32</v>
@@ -5318,43 +5309,43 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" t="s">
         <v>272</v>
       </c>
       <c r="C66" t="s">
-        <v>273</v>
+        <v>89</v>
       </c>
       <c r="D66" t="s">
-        <v>45</v>
+        <v>247</v>
       </c>
       <c r="E66" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F66" t="s">
         <v>55</v>
       </c>
       <c r="G66" t="s">
+        <v>273</v>
+      </c>
+      <c r="H66" t="s">
+        <v>273</v>
+      </c>
+      <c r="K66">
+        <v>49.164062000000001</v>
+      </c>
+      <c r="L66">
+        <v>-123.126351</v>
+      </c>
+      <c r="M66" t="s">
         <v>274</v>
       </c>
-      <c r="H66" t="s">
-        <v>274</v>
-      </c>
-      <c r="K66">
-        <v>49.156863000000001</v>
-      </c>
-      <c r="L66">
-        <v>-123.139976</v>
-      </c>
-      <c r="M66" t="s">
-        <v>275</v>
-      </c>
       <c r="N66">
-        <v>49.179198300000003</v>
+        <v>49.178049299999998</v>
       </c>
       <c r="O66">
-        <v>-123.1249191</v>
+        <v>-123.13184800000001</v>
       </c>
       <c r="P66" t="s">
         <v>32</v>
@@ -5365,19 +5356,16 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B67" t="s">
+        <v>275</v>
+      </c>
+      <c r="C67" t="s">
         <v>276</v>
       </c>
-      <c r="C67" t="s">
-        <v>93</v>
-      </c>
-      <c r="D67" t="s">
-        <v>251</v>
-      </c>
       <c r="E67" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F67" t="s">
         <v>55</v>
@@ -5389,19 +5377,19 @@
         <v>277</v>
       </c>
       <c r="K67">
-        <v>49.164062000000001</v>
+        <v>49.183202000000001</v>
       </c>
       <c r="L67">
-        <v>-123.126351</v>
+        <v>-123.13476799999999</v>
       </c>
       <c r="M67" t="s">
         <v>278</v>
       </c>
       <c r="N67">
-        <v>49.178049299999998</v>
+        <v>49.186371700000002</v>
       </c>
       <c r="O67">
-        <v>-123.13184800000001</v>
+        <v>-123.1328771</v>
       </c>
       <c r="P67" t="s">
         <v>32</v>
@@ -5412,7 +5400,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
         <v>279</v>
@@ -5420,11 +5408,14 @@
       <c r="C68" t="s">
         <v>280</v>
       </c>
+      <c r="D68" t="s">
+        <v>45</v>
+      </c>
       <c r="E68" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F68" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G68" t="s">
         <v>281</v>
@@ -5433,19 +5424,19 @@
         <v>281</v>
       </c>
       <c r="K68">
-        <v>49.183202000000001</v>
+        <v>49.190268000000003</v>
       </c>
       <c r="L68">
-        <v>-123.13476799999999</v>
+        <v>-123.171948</v>
       </c>
       <c r="M68" t="s">
         <v>282</v>
       </c>
       <c r="N68">
-        <v>49.186371700000002</v>
+        <v>49.179043700000001</v>
       </c>
       <c r="O68">
-        <v>-123.1328771</v>
+        <v>-123.132358</v>
       </c>
       <c r="P68" t="s">
         <v>32</v>
@@ -5456,19 +5447,19 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" t="s">
         <v>283</v>
       </c>
       <c r="C69" t="s">
+        <v>243</v>
+      </c>
+      <c r="D69" t="s">
         <v>284</v>
       </c>
-      <c r="D69" t="s">
-        <v>45</v>
-      </c>
       <c r="E69" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F69" t="s">
         <v>21</v>
@@ -5480,19 +5471,19 @@
         <v>285</v>
       </c>
       <c r="K69">
-        <v>49.190268000000003</v>
+        <v>49.097625999999998</v>
       </c>
       <c r="L69">
-        <v>-123.171948</v>
+        <v>-123.102493</v>
       </c>
       <c r="M69" t="s">
         <v>286</v>
       </c>
       <c r="N69">
-        <v>49.179043700000001</v>
+        <v>49.193171200000002</v>
       </c>
       <c r="O69">
-        <v>-123.132358</v>
+        <v>-123.1297562</v>
       </c>
       <c r="P69" t="s">
         <v>32</v>
@@ -5503,43 +5494,43 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
         <v>287</v>
       </c>
       <c r="C70" t="s">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="D70" t="s">
+        <v>45</v>
+      </c>
+      <c r="E70" t="s">
+        <v>182</v>
+      </c>
+      <c r="F70" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" t="s">
         <v>288</v>
       </c>
-      <c r="E70" t="s">
-        <v>186</v>
-      </c>
-      <c r="F70" t="s">
-        <v>21</v>
-      </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
+        <v>288</v>
+      </c>
+      <c r="K70">
+        <v>49.315494999999999</v>
+      </c>
+      <c r="L70">
+        <v>-123.06486700000001</v>
+      </c>
+      <c r="M70" t="s">
         <v>289</v>
       </c>
-      <c r="H70" t="s">
-        <v>289</v>
-      </c>
-      <c r="K70">
-        <v>49.097625999999998</v>
-      </c>
-      <c r="L70">
-        <v>-123.102493</v>
-      </c>
-      <c r="M70" t="s">
-        <v>290</v>
-      </c>
       <c r="N70">
-        <v>49.193171200000002</v>
+        <v>49.185653500000001</v>
       </c>
       <c r="O70">
-        <v>-123.1297562</v>
+        <v>-123.129079</v>
       </c>
       <c r="P70" t="s">
         <v>32</v>
@@ -5550,43 +5541,40 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B71" t="s">
+        <v>290</v>
+      </c>
+      <c r="C71" t="s">
+        <v>276</v>
+      </c>
+      <c r="E71" t="s">
+        <v>182</v>
+      </c>
+      <c r="F71" t="s">
+        <v>55</v>
+      </c>
+      <c r="G71" t="s">
         <v>291</v>
       </c>
-      <c r="C71" t="s">
-        <v>77</v>
-      </c>
-      <c r="D71" t="s">
-        <v>45</v>
-      </c>
-      <c r="E71" t="s">
-        <v>186</v>
-      </c>
-      <c r="F71" t="s">
-        <v>21</v>
-      </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
+        <v>291</v>
+      </c>
+      <c r="K71">
+        <v>49.179955</v>
+      </c>
+      <c r="L71">
+        <v>-123.13707599999999</v>
+      </c>
+      <c r="M71" t="s">
         <v>292</v>
       </c>
-      <c r="H71" t="s">
-        <v>292</v>
-      </c>
-      <c r="K71">
-        <v>49.315494999999999</v>
-      </c>
-      <c r="L71">
-        <v>-123.06486700000001</v>
-      </c>
-      <c r="M71" t="s">
-        <v>293</v>
-      </c>
       <c r="N71">
-        <v>49.185653500000001</v>
+        <v>49.181539700000002</v>
       </c>
       <c r="O71">
-        <v>-123.129079</v>
+        <v>-123.1359355</v>
       </c>
       <c r="P71" t="s">
         <v>32</v>
@@ -5597,43 +5585,46 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B72" t="s">
+        <v>293</v>
+      </c>
+      <c r="C72" t="s">
+        <v>133</v>
+      </c>
+      <c r="D72" t="s">
+        <v>54</v>
+      </c>
+      <c r="E72" t="s">
+        <v>182</v>
+      </c>
+      <c r="F72" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72" t="s">
         <v>294</v>
       </c>
-      <c r="C72" t="s">
-        <v>280</v>
-      </c>
-      <c r="E72" t="s">
-        <v>186</v>
-      </c>
-      <c r="F72" t="s">
-        <v>55</v>
-      </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
+        <v>294</v>
+      </c>
+      <c r="K72">
+        <v>49.317605</v>
+      </c>
+      <c r="L72">
+        <v>-122.922433</v>
+      </c>
+      <c r="M72" t="s">
         <v>295</v>
       </c>
-      <c r="H72" t="s">
-        <v>295</v>
-      </c>
-      <c r="K72">
-        <v>49.179955</v>
-      </c>
-      <c r="L72">
-        <v>-123.13707599999999</v>
-      </c>
-      <c r="M72" t="s">
-        <v>296</v>
-      </c>
       <c r="N72">
-        <v>49.181539700000002</v>
+        <v>49.1667749</v>
       </c>
       <c r="O72">
-        <v>-123.1359355</v>
+        <v>-123.138175</v>
       </c>
       <c r="P72" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q72" t="s">
         <v>26</v>
@@ -5641,19 +5632,19 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B73" t="s">
+        <v>296</v>
+      </c>
+      <c r="C73" t="s">
         <v>297</v>
       </c>
-      <c r="C73" t="s">
-        <v>137</v>
-      </c>
       <c r="D73" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E73" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F73" t="s">
         <v>21</v>
@@ -5665,22 +5656,22 @@
         <v>298</v>
       </c>
       <c r="K73">
-        <v>49.317605</v>
+        <v>49.206167999999998</v>
       </c>
       <c r="L73">
-        <v>-122.922433</v>
+        <v>-122.890783</v>
       </c>
       <c r="M73" t="s">
         <v>299</v>
       </c>
       <c r="N73">
-        <v>49.1667749</v>
+        <v>49.233198100000003</v>
       </c>
       <c r="O73">
-        <v>-123.138175</v>
+        <v>-123.0344772</v>
       </c>
       <c r="P73" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q73" t="s">
         <v>26</v>
@@ -5688,7 +5679,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" t="s">
         <v>300</v>
@@ -5696,11 +5687,8 @@
       <c r="C74" t="s">
         <v>301</v>
       </c>
-      <c r="D74" t="s">
-        <v>45</v>
-      </c>
       <c r="E74" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F74" t="s">
         <v>21</v>
@@ -5712,22 +5700,22 @@
         <v>302</v>
       </c>
       <c r="K74">
-        <v>49.206167999999998</v>
+        <v>49.163316000000002</v>
       </c>
       <c r="L74">
-        <v>-122.890783</v>
+        <v>-123.027629</v>
       </c>
       <c r="M74" t="s">
         <v>303</v>
       </c>
       <c r="N74">
-        <v>49.233198100000003</v>
+        <v>49.178775999999999</v>
       </c>
       <c r="O74">
-        <v>-123.0344772</v>
+        <v>-123.1279696</v>
       </c>
       <c r="P74" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q74" t="s">
         <v>26</v>
@@ -5735,7 +5723,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
         <v>304</v>
@@ -5743,11 +5731,14 @@
       <c r="C75" t="s">
         <v>305</v>
       </c>
+      <c r="D75" t="s">
+        <v>45</v>
+      </c>
       <c r="E75" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F75" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G75" t="s">
         <v>306</v>
@@ -5756,22 +5747,22 @@
         <v>306</v>
       </c>
       <c r="K75">
-        <v>49.163316000000002</v>
+        <v>49.275596</v>
       </c>
       <c r="L75">
-        <v>-123.027629</v>
+        <v>-123.11138800000001</v>
       </c>
       <c r="M75" t="s">
         <v>307</v>
       </c>
       <c r="N75">
-        <v>44.584708900000003</v>
+        <v>49.231740100000003</v>
       </c>
       <c r="O75">
-        <v>-122.3559609</v>
+        <v>-123.11961700000001</v>
       </c>
       <c r="P75" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q75" t="s">
         <v>26</v>
@@ -5779,43 +5770,46 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C76" t="s">
-        <v>305</v>
+        <v>77</v>
+      </c>
+      <c r="D76" t="s">
+        <v>117</v>
       </c>
       <c r="E76" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F76" t="s">
         <v>21</v>
       </c>
       <c r="G76" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H76" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K76">
-        <v>49.163316000000002</v>
+        <v>49.182631000000001</v>
       </c>
       <c r="L76">
-        <v>-123.027629</v>
+        <v>-123.15247599999999</v>
       </c>
       <c r="M76" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="N76">
-        <v>44.584708900000003</v>
+        <v>49.283182699999998</v>
       </c>
       <c r="O76">
-        <v>-122.3559609</v>
+        <v>-123.10302660000001</v>
       </c>
       <c r="P76" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q76" t="s">
         <v>26</v>
@@ -5823,43 +5817,43 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C77" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D77" t="s">
         <v>45</v>
       </c>
       <c r="E77" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F77" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G77" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="H77" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K77">
-        <v>49.275596</v>
+        <v>49.321486999999998</v>
       </c>
       <c r="L77">
-        <v>-123.11138800000001</v>
+        <v>-122.96035500000001</v>
       </c>
       <c r="M77" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N77">
-        <v>49.231740100000003</v>
+        <v>49.263333299999999</v>
       </c>
       <c r="O77">
-        <v>-123.11961700000001</v>
+        <v>-123.1327344</v>
       </c>
       <c r="P77" t="s">
         <v>32</v>
@@ -5870,43 +5864,43 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C78" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="E78" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F78" t="s">
         <v>21</v>
       </c>
       <c r="G78" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H78" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K78">
-        <v>49.182631000000001</v>
+        <v>49.354115999999998</v>
       </c>
       <c r="L78">
-        <v>-123.15247599999999</v>
+        <v>-123.093879</v>
       </c>
       <c r="M78" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="N78">
-        <v>49.283182699999998</v>
+        <v>49.267035999999997</v>
       </c>
       <c r="O78">
-        <v>-123.10302660000001</v>
+        <v>-123.09258920000001</v>
       </c>
       <c r="P78" t="s">
         <v>32</v>
@@ -5917,46 +5911,46 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C79" t="s">
-        <v>316</v>
+        <v>77</v>
       </c>
       <c r="D79" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="E79" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F79" t="s">
         <v>21</v>
       </c>
       <c r="G79" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H79" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K79">
-        <v>49.321486999999998</v>
+        <v>49.147655</v>
       </c>
       <c r="L79">
-        <v>-122.96035500000001</v>
+        <v>-123.25106599999999</v>
       </c>
       <c r="M79" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N79">
-        <v>49.263333299999999</v>
+        <v>49.270571099999998</v>
       </c>
       <c r="O79">
-        <v>-123.1327344</v>
+        <v>-123.15030299999999</v>
       </c>
       <c r="P79" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q79" t="s">
         <v>26</v>
@@ -5964,43 +5958,43 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C80" t="s">
-        <v>137</v>
+        <v>322</v>
       </c>
       <c r="D80" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E80" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F80" t="s">
         <v>21</v>
       </c>
       <c r="G80" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H80" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K80">
-        <v>49.354115999999998</v>
+        <v>49.309575000000002</v>
       </c>
       <c r="L80">
-        <v>-123.093879</v>
+        <v>-123.23798499999999</v>
       </c>
       <c r="M80" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N80">
-        <v>49.267035999999997</v>
+        <v>49.267270799999999</v>
       </c>
       <c r="O80">
-        <v>-123.09258920000001</v>
+        <v>-123.1130886</v>
       </c>
       <c r="P80" t="s">
         <v>32</v>
@@ -6011,46 +6005,43 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C81" t="s">
-        <v>77</v>
-      </c>
-      <c r="D81" t="s">
-        <v>121</v>
+        <v>326</v>
       </c>
       <c r="E81" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F81" t="s">
         <v>21</v>
       </c>
       <c r="G81" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="H81" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K81">
-        <v>49.147655</v>
+        <v>49.273527999999999</v>
       </c>
       <c r="L81">
-        <v>-123.25106599999999</v>
+        <v>-123.166693</v>
       </c>
       <c r="M81" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="N81">
-        <v>49.270571099999998</v>
+        <v>49.2683708</v>
       </c>
       <c r="O81">
-        <v>-123.15030299999999</v>
+        <v>-123.1539745</v>
       </c>
       <c r="P81" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q81" t="s">
         <v>26</v>
@@ -6058,43 +6049,40 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C82" t="s">
-        <v>326</v>
-      </c>
-      <c r="D82" t="s">
-        <v>45</v>
+        <v>330</v>
       </c>
       <c r="E82" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F82" t="s">
         <v>21</v>
       </c>
       <c r="G82" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H82" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="K82">
-        <v>49.309575000000002</v>
+        <v>49.293007000000003</v>
       </c>
       <c r="L82">
-        <v>-123.23798499999999</v>
+        <v>-122.912181</v>
       </c>
       <c r="M82" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="N82">
-        <v>49.267270799999999</v>
+        <v>38.83081</v>
       </c>
       <c r="O82">
-        <v>-123.1130886</v>
+        <v>-77.188449800000001</v>
       </c>
       <c r="P82" t="s">
         <v>32</v>
@@ -6105,43 +6093,46 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C83" t="s">
-        <v>330</v>
+        <v>334</v>
+      </c>
+      <c r="D83" t="s">
+        <v>45</v>
       </c>
       <c r="E83" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F83" t="s">
         <v>21</v>
       </c>
       <c r="G83" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H83" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="K83">
-        <v>49.273527999999999</v>
+        <v>49.218820000000001</v>
       </c>
       <c r="L83">
-        <v>-123.166693</v>
+        <v>-123.06908300000001</v>
       </c>
       <c r="M83" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="N83">
-        <v>49.2683708</v>
+        <v>34.062860299999997</v>
       </c>
       <c r="O83">
-        <v>-123.1539745</v>
+        <v>-118.14672179999999</v>
       </c>
       <c r="P83" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q83" t="s">
         <v>26</v>
@@ -6149,43 +6140,46 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C84" t="s">
-        <v>334</v>
+        <v>338</v>
+      </c>
+      <c r="D84" t="s">
+        <v>262</v>
       </c>
       <c r="E84" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F84" t="s">
         <v>21</v>
       </c>
       <c r="G84" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H84" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="K84">
-        <v>49.293007000000003</v>
+        <v>49.328156</v>
       </c>
       <c r="L84">
-        <v>-122.912181</v>
+        <v>-122.852121</v>
       </c>
       <c r="M84" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="N84">
-        <v>38.83081</v>
+        <v>34.056002599999999</v>
       </c>
       <c r="O84">
-        <v>-77.188449800000001</v>
+        <v>-118.3124909</v>
       </c>
       <c r="P84" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q84" t="s">
         <v>26</v>
@@ -6193,46 +6187,46 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C85" t="s">
-        <v>338</v>
+        <v>28</v>
       </c>
       <c r="D85" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>186</v>
+        <v>342</v>
       </c>
       <c r="F85" t="s">
         <v>21</v>
       </c>
       <c r="G85" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H85" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K85">
-        <v>49.218820000000001</v>
+        <v>34.179929000000001</v>
       </c>
       <c r="L85">
-        <v>-123.06908300000001</v>
+        <v>-118.263172</v>
       </c>
       <c r="M85" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="N85">
-        <v>34.062860299999997</v>
+        <v>34.048146500000001</v>
       </c>
       <c r="O85">
-        <v>-118.14672179999999</v>
+        <v>-118.2560174</v>
       </c>
       <c r="P85" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q85" t="s">
         <v>26</v>
@@ -6240,46 +6234,46 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D86" t="s">
+        <v>173</v>
+      </c>
+      <c r="E86" t="s">
         <v>342</v>
       </c>
-      <c r="D86" t="s">
-        <v>266</v>
-      </c>
-      <c r="E86" t="s">
-        <v>186</v>
-      </c>
       <c r="F86" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G86" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H86" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K86">
-        <v>49.328156</v>
+        <v>34.046357</v>
       </c>
       <c r="L86">
-        <v>-122.852121</v>
+        <v>-118.239452</v>
       </c>
       <c r="M86" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N86">
-        <v>34.056002599999999</v>
+        <v>34.051038800000001</v>
       </c>
       <c r="O86">
-        <v>-118.3124909</v>
+        <v>-118.2557575</v>
       </c>
       <c r="P86" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q86" t="s">
         <v>26</v>
@@ -6287,43 +6281,43 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>349</v>
       </c>
       <c r="D87" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E87" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F87" t="s">
         <v>21</v>
       </c>
       <c r="G87" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H87" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K87">
-        <v>34.179929000000001</v>
+        <v>34.123168999999997</v>
       </c>
       <c r="L87">
-        <v>-118.263172</v>
+        <v>-118.17034</v>
       </c>
       <c r="M87" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N87">
-        <v>34.048146500000001</v>
+        <v>34.039315000000002</v>
       </c>
       <c r="O87">
-        <v>-118.2560174</v>
+        <v>-118.258852</v>
       </c>
       <c r="P87" t="s">
         <v>32</v>
@@ -6334,43 +6328,43 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C88" t="s">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="E88" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F88" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K88">
-        <v>34.046357</v>
+        <v>34.077306999999998</v>
       </c>
       <c r="L88">
-        <v>-118.239452</v>
+        <v>-118.188006</v>
       </c>
       <c r="M88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="N88">
-        <v>34.051038800000001</v>
+        <v>34.050204999999998</v>
       </c>
       <c r="O88">
-        <v>-118.2557575</v>
+        <v>-118.2569793</v>
       </c>
       <c r="P88" t="s">
         <v>32</v>
@@ -6381,43 +6375,43 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C89" t="s">
-        <v>353</v>
+        <v>133</v>
       </c>
       <c r="D89" t="s">
-        <v>45</v>
+        <v>356</v>
       </c>
       <c r="E89" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F89" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G89" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H89" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K89">
-        <v>34.123168999999997</v>
+        <v>34.102119999999999</v>
       </c>
       <c r="L89">
-        <v>-118.17034</v>
+        <v>-118.05902</v>
       </c>
       <c r="M89" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N89">
-        <v>34.039315000000002</v>
+        <v>34.105415899999997</v>
       </c>
       <c r="O89">
-        <v>-118.258852</v>
+        <v>-118.0744894</v>
       </c>
       <c r="P89" t="s">
         <v>32</v>
@@ -6428,43 +6422,43 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C90" t="s">
-        <v>18</v>
+        <v>360</v>
       </c>
       <c r="D90" t="s">
-        <v>94</v>
+        <v>361</v>
       </c>
       <c r="E90" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F90" t="s">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="G90" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="H90" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="K90">
-        <v>34.077306999999998</v>
+        <v>34.0383</v>
       </c>
       <c r="L90">
-        <v>-118.188006</v>
+        <v>-118.256</v>
       </c>
       <c r="M90" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="N90">
-        <v>34.050204999999998</v>
+        <v>34.038559900000003</v>
       </c>
       <c r="O90">
-        <v>-118.2569793</v>
+        <v>-118.25829</v>
       </c>
       <c r="P90" t="s">
         <v>32</v>
@@ -6475,43 +6469,43 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C91" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="D91" t="s">
-        <v>360</v>
+        <v>147</v>
       </c>
       <c r="E91" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F91" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G91" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H91" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K91">
-        <v>34.102119999999999</v>
+        <v>34.059592000000002</v>
       </c>
       <c r="L91">
-        <v>-118.05902</v>
+        <v>-118.22751100000001</v>
       </c>
       <c r="M91" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="N91">
-        <v>34.105415899999997</v>
+        <v>34.115996799999998</v>
       </c>
       <c r="O91">
-        <v>-118.0744894</v>
+        <v>-118.23595520000001</v>
       </c>
       <c r="P91" t="s">
         <v>32</v>
@@ -6522,43 +6516,40 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C92" t="s">
-        <v>364</v>
-      </c>
-      <c r="D92" t="s">
-        <v>365</v>
+        <v>108</v>
       </c>
       <c r="E92" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F92" t="s">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="G92" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H92" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K92">
-        <v>34.0383</v>
+        <v>34.061891000000003</v>
       </c>
       <c r="L92">
-        <v>-118.256</v>
+        <v>-118.042399</v>
       </c>
       <c r="M92" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N92">
-        <v>34.038559900000003</v>
+        <v>34.146571600000001</v>
       </c>
       <c r="O92">
-        <v>-118.25829</v>
+        <v>-118.14782719999999</v>
       </c>
       <c r="P92" t="s">
         <v>32</v>
@@ -6569,43 +6560,40 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C93" t="s">
-        <v>34</v>
-      </c>
-      <c r="D93" t="s">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="E93" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F93" t="s">
         <v>21</v>
       </c>
       <c r="G93" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H93" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K93">
-        <v>34.059592000000002</v>
+        <v>34.139347000000001</v>
       </c>
       <c r="L93">
-        <v>-118.22751100000001</v>
+        <v>-118.27474599999999</v>
       </c>
       <c r="M93" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N93">
-        <v>34.115996799999998</v>
+        <v>34.144800199999999</v>
       </c>
       <c r="O93">
-        <v>-118.23595520000001</v>
+        <v>-118.1241775</v>
       </c>
       <c r="P93" t="s">
         <v>32</v>
@@ -6616,40 +6604,40 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="E94" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F94" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G94" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H94" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K94">
-        <v>34.061891000000003</v>
+        <v>34.153027999999999</v>
       </c>
       <c r="L94">
-        <v>-118.042399</v>
+        <v>-118.134512</v>
       </c>
       <c r="M94" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N94">
-        <v>34.146571600000001</v>
+        <v>34.146235900000001</v>
       </c>
       <c r="O94">
-        <v>-118.14782719999999</v>
+        <v>-118.11592589999999</v>
       </c>
       <c r="P94" t="s">
         <v>32</v>
@@ -6660,40 +6648,40 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C95" t="s">
         <v>68</v>
       </c>
       <c r="E95" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F95" t="s">
         <v>21</v>
       </c>
       <c r="G95" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H95" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K95">
-        <v>34.139347000000001</v>
+        <v>34.062057000000003</v>
       </c>
       <c r="L95">
-        <v>-118.27474599999999</v>
+        <v>-118.22735299999999</v>
       </c>
       <c r="M95" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N95">
-        <v>34.144800199999999</v>
+        <v>34.146282499999998</v>
       </c>
       <c r="O95">
-        <v>-118.1241775</v>
+        <v>-118.1197315</v>
       </c>
       <c r="P95" t="s">
         <v>32</v>
@@ -6704,40 +6692,40 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C96" t="s">
-        <v>68</v>
+        <v>381</v>
       </c>
       <c r="E96" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F96" t="s">
         <v>55</v>
       </c>
       <c r="G96" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H96" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="K96">
-        <v>34.153027999999999</v>
+        <v>34.149583999999997</v>
       </c>
       <c r="L96">
-        <v>-118.134512</v>
+        <v>-118.142777</v>
       </c>
       <c r="M96" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="N96">
-        <v>34.146235900000001</v>
+        <v>34.144700800000003</v>
       </c>
       <c r="O96">
-        <v>-118.11592589999999</v>
+        <v>-118.1288098</v>
       </c>
       <c r="P96" t="s">
         <v>32</v>
@@ -6748,40 +6736,43 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C97" t="s">
-        <v>68</v>
+        <v>133</v>
+      </c>
+      <c r="D97" t="s">
+        <v>54</v>
       </c>
       <c r="E97" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F97" t="s">
         <v>21</v>
       </c>
       <c r="G97" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H97" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K97">
-        <v>34.062057000000003</v>
+        <v>33.974836000000003</v>
       </c>
       <c r="L97">
-        <v>-118.22735299999999</v>
+        <v>-118.293626</v>
       </c>
       <c r="M97" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N97">
-        <v>34.146282499999998</v>
+        <v>34.146697899999999</v>
       </c>
       <c r="O97">
-        <v>-118.1197315</v>
+        <v>-118.1485783</v>
       </c>
       <c r="P97" t="s">
         <v>32</v>
@@ -6792,40 +6783,43 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C98" t="s">
-        <v>385</v>
+        <v>388</v>
+      </c>
+      <c r="D98" t="s">
+        <v>45</v>
       </c>
       <c r="E98" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F98" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G98" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="H98" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="K98">
-        <v>34.149583999999997</v>
+        <v>34.096387</v>
       </c>
       <c r="L98">
-        <v>-118.142777</v>
+        <v>-118.18050599999999</v>
       </c>
       <c r="M98" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N98">
-        <v>34.144700800000003</v>
+        <v>34.1447517</v>
       </c>
       <c r="O98">
-        <v>-118.1288098</v>
+        <v>-118.1490544</v>
       </c>
       <c r="P98" t="s">
         <v>32</v>
@@ -6836,43 +6830,43 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C99" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="D99" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F99" t="s">
         <v>21</v>
       </c>
       <c r="G99" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H99" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K99">
-        <v>33.974836000000003</v>
+        <v>34.043351000000001</v>
       </c>
       <c r="L99">
-        <v>-118.293626</v>
+        <v>-118.00763499999999</v>
       </c>
       <c r="M99" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="N99">
-        <v>34.146697899999999</v>
+        <v>34.146623400000003</v>
       </c>
       <c r="O99">
-        <v>-118.1485783</v>
+        <v>-118.1478274</v>
       </c>
       <c r="P99" t="s">
         <v>32</v>
@@ -6883,43 +6877,43 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C100" t="s">
-        <v>392</v>
+        <v>133</v>
       </c>
       <c r="D100" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E100" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F100" t="s">
         <v>21</v>
       </c>
       <c r="G100" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H100" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K100">
-        <v>34.096387</v>
+        <v>33.995131999999998</v>
       </c>
       <c r="L100">
-        <v>-118.18050599999999</v>
+        <v>-118.165395</v>
       </c>
       <c r="M100" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N100">
-        <v>34.1447517</v>
+        <v>34.142311499999998</v>
       </c>
       <c r="O100">
-        <v>-118.1490544</v>
+        <v>-118.14197799999999</v>
       </c>
       <c r="P100" t="s">
         <v>32</v>
@@ -6930,43 +6924,43 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C101" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="D101" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="E101" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F101" t="s">
         <v>21</v>
       </c>
       <c r="G101" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H101" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K101">
-        <v>34.043351000000001</v>
+        <v>34.153775000000003</v>
       </c>
       <c r="L101">
-        <v>-118.00763499999999</v>
+        <v>-118.14360600000001</v>
       </c>
       <c r="M101" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N101">
-        <v>34.146623400000003</v>
+        <v>34.049991599999998</v>
       </c>
       <c r="O101">
-        <v>-118.1478274</v>
+        <v>-118.2493879</v>
       </c>
       <c r="P101" t="s">
         <v>32</v>
@@ -6977,43 +6971,43 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C102" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="D102" t="s">
-        <v>54</v>
+        <v>401</v>
       </c>
       <c r="E102" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F102" t="s">
         <v>21</v>
       </c>
       <c r="G102" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H102" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K102">
-        <v>33.995131999999998</v>
+        <v>34.014543000000003</v>
       </c>
       <c r="L102">
-        <v>-118.165395</v>
+        <v>-117.98232</v>
       </c>
       <c r="M102" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N102">
-        <v>34.142311499999998</v>
+        <v>34.063971899999999</v>
       </c>
       <c r="O102">
-        <v>-118.14197799999999</v>
+        <v>-118.29679899999999</v>
       </c>
       <c r="P102" t="s">
         <v>32</v>
@@ -7024,43 +7018,43 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C103" t="s">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="D103" t="s">
-        <v>85</v>
+        <v>406</v>
       </c>
       <c r="E103" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F103" t="s">
         <v>21</v>
       </c>
       <c r="G103" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="H103" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="K103">
-        <v>34.153775000000003</v>
+        <v>34.032609000000001</v>
       </c>
       <c r="L103">
-        <v>-118.14360600000001</v>
+        <v>-118.313913</v>
       </c>
       <c r="M103" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="N103">
-        <v>34.049991599999998</v>
+        <v>34.050555899999999</v>
       </c>
       <c r="O103">
-        <v>-118.2493879</v>
+        <v>-118.3087721</v>
       </c>
       <c r="P103" t="s">
         <v>32</v>
@@ -7071,43 +7065,43 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C104" t="s">
-        <v>18</v>
+        <v>405</v>
       </c>
       <c r="D104" t="s">
-        <v>405</v>
+        <v>85</v>
       </c>
       <c r="E104" t="s">
-        <v>346</v>
+        <v>410</v>
       </c>
       <c r="F104" t="s">
         <v>21</v>
       </c>
       <c r="G104" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H104" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="K104">
-        <v>34.014543000000003</v>
+        <v>41.898941000000001</v>
       </c>
       <c r="L104">
-        <v>-117.98232</v>
+        <v>-87.645972999999998</v>
       </c>
       <c r="M104" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="N104">
-        <v>34.063971899999999</v>
+        <v>34.057505499999998</v>
       </c>
       <c r="O104">
-        <v>-118.29679899999999</v>
+        <v>-118.3058059</v>
       </c>
       <c r="P104" t="s">
         <v>32</v>
@@ -7118,43 +7112,43 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C105" t="s">
-        <v>409</v>
+        <v>172</v>
       </c>
       <c r="D105" t="s">
+        <v>414</v>
+      </c>
+      <c r="E105" t="s">
         <v>410</v>
       </c>
-      <c r="E105" t="s">
-        <v>346</v>
-      </c>
       <c r="F105" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G105" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H105" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K105">
-        <v>34.032609000000001</v>
+        <v>41.880468999999998</v>
       </c>
       <c r="L105">
-        <v>-118.313913</v>
+        <v>-87.628934999999998</v>
       </c>
       <c r="M105" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="N105">
-        <v>34.050555899999999</v>
+        <v>41.903352599999998</v>
       </c>
       <c r="O105">
-        <v>-118.3087721</v>
+        <v>-87.676410000000004</v>
       </c>
       <c r="P105" t="s">
         <v>32</v>
@@ -7165,43 +7159,43 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C106" t="s">
-        <v>409</v>
+        <v>226</v>
       </c>
       <c r="D106" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="E106" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F106" t="s">
         <v>21</v>
       </c>
       <c r="G106" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H106" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K106">
-        <v>41.898941000000001</v>
+        <v>41.917304999999999</v>
       </c>
       <c r="L106">
-        <v>-87.645972999999998</v>
+        <v>-87.688873000000001</v>
       </c>
       <c r="M106" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N106">
-        <v>34.057505499999998</v>
+        <v>41.920079800000003</v>
       </c>
       <c r="O106">
-        <v>-118.3058059</v>
+        <v>-87.662618199999997</v>
       </c>
       <c r="P106" t="s">
         <v>32</v>
@@ -7212,43 +7206,43 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C107" t="s">
-        <v>176</v>
+        <v>421</v>
       </c>
       <c r="D107" t="s">
-        <v>418</v>
+        <v>257</v>
       </c>
       <c r="E107" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F107" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G107" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="H107" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K107">
-        <v>41.880468999999998</v>
+        <v>41.855924000000002</v>
       </c>
       <c r="L107">
-        <v>-87.628934999999998</v>
+        <v>-87.735781000000003</v>
       </c>
       <c r="M107" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="N107">
-        <v>41.903352599999998</v>
+        <v>41.953502800000003</v>
       </c>
       <c r="O107">
-        <v>-87.676410000000004</v>
+        <v>-87.678035699999995</v>
       </c>
       <c r="P107" t="s">
         <v>32</v>
@@ -7259,43 +7253,43 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C108" t="s">
-        <v>230</v>
+        <v>405</v>
       </c>
       <c r="D108" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E108" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F108" t="s">
         <v>21</v>
       </c>
       <c r="G108" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="H108" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K108">
-        <v>41.917304999999999</v>
+        <v>41.903550000000003</v>
       </c>
       <c r="L108">
-        <v>-87.688873000000001</v>
+        <v>-87.599154999999996</v>
       </c>
       <c r="M108" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N108">
-        <v>41.920079800000003</v>
+        <v>41.969358999999997</v>
       </c>
       <c r="O108">
-        <v>-87.662618199999997</v>
+        <v>-87.7080737</v>
       </c>
       <c r="P108" t="s">
         <v>32</v>
@@ -7306,43 +7300,43 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C109" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D109" t="s">
-        <v>261</v>
+        <v>54</v>
       </c>
       <c r="E109" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F109" t="s">
         <v>21</v>
       </c>
       <c r="G109" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="H109" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K109">
-        <v>41.855924000000002</v>
+        <v>41.896870999999997</v>
       </c>
       <c r="L109">
-        <v>-87.735781000000003</v>
+        <v>-87.628934999999998</v>
       </c>
       <c r="M109" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N109">
-        <v>41.953502800000003</v>
+        <v>41.965855599999998</v>
       </c>
       <c r="O109">
-        <v>-87.678035699999995</v>
+        <v>-87.708724200000006</v>
       </c>
       <c r="P109" t="s">
         <v>32</v>
@@ -7353,43 +7347,43 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C110" t="s">
-        <v>409</v>
+        <v>133</v>
       </c>
       <c r="D110" t="s">
         <v>54</v>
       </c>
       <c r="E110" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F110" t="s">
         <v>21</v>
       </c>
       <c r="G110" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H110" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="K110">
-        <v>41.903550000000003</v>
+        <v>41.787467999999997</v>
       </c>
       <c r="L110">
-        <v>-87.599154999999996</v>
+        <v>-87.671238000000002</v>
       </c>
       <c r="M110" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="N110">
-        <v>41.969358999999997</v>
+        <v>41.9686047</v>
       </c>
       <c r="O110">
-        <v>-87.7080737</v>
+        <v>-87.708653499999997</v>
       </c>
       <c r="P110" t="s">
         <v>32</v>
@@ -7400,43 +7394,43 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C111" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D111" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E111" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F111" t="s">
         <v>21</v>
       </c>
       <c r="G111" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="H111" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="K111">
-        <v>41.896870999999997</v>
+        <v>41.769176999999999</v>
       </c>
       <c r="L111">
-        <v>-87.628934999999998</v>
+        <v>-87.631034</v>
       </c>
       <c r="M111" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N111">
-        <v>41.965855599999998</v>
+        <v>41.968724000000002</v>
       </c>
       <c r="O111">
-        <v>-87.708724200000006</v>
+        <v>-87.716641999999993</v>
       </c>
       <c r="P111" t="s">
         <v>32</v>
@@ -7447,43 +7441,43 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C112" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="D112" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E112" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F112" t="s">
         <v>21</v>
       </c>
       <c r="G112" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="H112" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K112">
-        <v>41.787467999999997</v>
+        <v>41.948723000000001</v>
       </c>
       <c r="L112">
-        <v>-87.671238000000002</v>
+        <v>-87.633274999999998</v>
       </c>
       <c r="M112" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="N112">
-        <v>41.9686047</v>
+        <v>41.917107799999997</v>
       </c>
       <c r="O112">
-        <v>-87.708653499999997</v>
+        <v>-87.687621500000006</v>
       </c>
       <c r="P112" t="s">
         <v>32</v>
@@ -7494,43 +7488,40 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C113" t="s">
-        <v>439</v>
-      </c>
-      <c r="D113" t="s">
-        <v>29</v>
+        <v>442</v>
       </c>
       <c r="E113" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F113" t="s">
         <v>21</v>
       </c>
       <c r="G113" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="H113" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K113">
-        <v>41.769176999999999</v>
+        <v>41.968077000000001</v>
       </c>
       <c r="L113">
-        <v>-87.631034</v>
+        <v>-87.730744999999999</v>
       </c>
       <c r="M113" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="N113">
-        <v>41.968724000000002</v>
+        <v>41.8787971</v>
       </c>
       <c r="O113">
-        <v>-87.716641999999993</v>
+        <v>-87.636495999999994</v>
       </c>
       <c r="P113" t="s">
         <v>32</v>
@@ -7541,46 +7532,43 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C114" t="s">
-        <v>28</v>
-      </c>
-      <c r="D114" t="s">
-        <v>29</v>
+        <v>446</v>
       </c>
       <c r="E114" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F114" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G114" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="H114" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="K114">
-        <v>41.948723000000001</v>
+        <v>41.879589000000003</v>
       </c>
       <c r="L114">
-        <v>-87.633274999999998</v>
+        <v>-87.628512999999998</v>
       </c>
       <c r="M114" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="N114">
-        <v>41.917107799999997</v>
+        <v>41.929807699999998</v>
       </c>
       <c r="O114">
-        <v>-87.687621500000006</v>
+        <v>-87.739138600000004</v>
       </c>
       <c r="P114" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q114" t="s">
         <v>26</v>
@@ -7588,43 +7576,46 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C115" t="s">
-        <v>446</v>
+        <v>450</v>
+      </c>
+      <c r="D115" t="s">
+        <v>284</v>
       </c>
       <c r="E115" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F115" t="s">
         <v>21</v>
       </c>
       <c r="G115" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H115" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K115">
-        <v>41.968077000000001</v>
+        <v>41.891987999999998</v>
       </c>
       <c r="L115">
-        <v>-87.730744999999999</v>
+        <v>-87.551186000000001</v>
       </c>
       <c r="M115" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N115">
-        <v>41.8787971</v>
+        <v>41.945089899999999</v>
       </c>
       <c r="O115">
-        <v>-87.636495999999994</v>
+        <v>-87.966997599999999</v>
       </c>
       <c r="P115" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q115" t="s">
         <v>26</v>
@@ -7632,43 +7623,46 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C116" t="s">
-        <v>450</v>
+        <v>435</v>
+      </c>
+      <c r="D116" t="s">
+        <v>54</v>
       </c>
       <c r="E116" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F116" t="s">
         <v>55</v>
       </c>
       <c r="G116" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="H116" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K116">
-        <v>41.879589000000003</v>
+        <v>41.873277000000002</v>
       </c>
       <c r="L116">
-        <v>-87.628512999999998</v>
+        <v>-87.622174000000001</v>
       </c>
       <c r="M116" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="N116">
-        <v>41.929807699999998</v>
+        <v>41.927503100000003</v>
       </c>
       <c r="O116">
-        <v>-87.739138600000004</v>
+        <v>-87.6513499</v>
       </c>
       <c r="P116" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q116" t="s">
         <v>26</v>
@@ -7676,46 +7670,46 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C117" t="s">
-        <v>454</v>
+        <v>28</v>
       </c>
       <c r="D117" t="s">
-        <v>288</v>
+        <v>54</v>
       </c>
       <c r="E117" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F117" t="s">
         <v>21</v>
       </c>
       <c r="G117" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H117" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K117">
-        <v>41.891987999999998</v>
+        <v>41.760624999999997</v>
       </c>
       <c r="L117">
-        <v>-87.551186000000001</v>
+        <v>-87.750223000000005</v>
       </c>
       <c r="M117" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N117">
-        <v>41.945089899999999</v>
+        <v>41.894661900000003</v>
       </c>
       <c r="O117">
-        <v>-87.966997599999999</v>
+        <v>-87.633989200000002</v>
       </c>
       <c r="P117" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q117" t="s">
         <v>26</v>
@@ -7723,43 +7717,43 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C118" t="s">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="D118" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
       <c r="E118" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F118" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G118" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H118" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K118">
-        <v>41.873277000000002</v>
+        <v>41.969507</v>
       </c>
       <c r="L118">
-        <v>-87.622174000000001</v>
+        <v>-87.865440000000007</v>
       </c>
       <c r="M118" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N118">
-        <v>41.927503100000003</v>
+        <v>41.895789299999997</v>
       </c>
       <c r="O118">
-        <v>-87.6513499</v>
+        <v>-87.671721000000005</v>
       </c>
       <c r="P118" t="s">
         <v>32</v>
@@ -7770,46 +7764,40 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C119" t="s">
         <v>28</v>
       </c>
       <c r="D119" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E119" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F119" t="s">
         <v>21</v>
       </c>
       <c r="G119" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H119" t="s">
-        <v>461</v>
-      </c>
-      <c r="K119">
-        <v>41.760624999999997</v>
-      </c>
-      <c r="L119">
-        <v>-87.750223000000005</v>
+        <v>463</v>
       </c>
       <c r="M119" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N119">
-        <v>41.894661900000003</v>
+        <v>41.7038206</v>
       </c>
       <c r="O119">
-        <v>-87.633989200000002</v>
+        <v>-87.801495299999999</v>
       </c>
       <c r="P119" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q119" t="s">
         <v>26</v>
@@ -7817,43 +7805,43 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C120" t="s">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="D120" t="s">
-        <v>177</v>
+        <v>54</v>
       </c>
       <c r="E120" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F120" t="s">
         <v>21</v>
       </c>
       <c r="G120" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H120" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K120">
-        <v>41.969507</v>
+        <v>42.005598999999997</v>
       </c>
       <c r="L120">
-        <v>-87.865440000000007</v>
+        <v>-87.782921000000002</v>
       </c>
       <c r="M120" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N120">
-        <v>41.895789299999997</v>
+        <v>41.927070499999999</v>
       </c>
       <c r="O120">
-        <v>-87.671721000000005</v>
+        <v>-87.641565499999999</v>
       </c>
       <c r="P120" t="s">
         <v>32</v>
@@ -7864,40 +7852,43 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C121" t="s">
-        <v>28</v>
-      </c>
-      <c r="D121" t="s">
-        <v>29</v>
+        <v>469</v>
       </c>
       <c r="E121" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F121" t="s">
         <v>21</v>
       </c>
       <c r="G121" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H121" t="s">
-        <v>467</v>
+        <v>470</v>
+      </c>
+      <c r="K121">
+        <v>41.959733999999997</v>
+      </c>
+      <c r="L121">
+        <v>-87.768660999999994</v>
       </c>
       <c r="M121" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="N121">
-        <v>41.7038206</v>
+        <v>41.886957099999997</v>
       </c>
       <c r="O121">
-        <v>-87.801495299999999</v>
+        <v>-87.651906400000001</v>
       </c>
       <c r="P121" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q121" t="s">
         <v>26</v>
@@ -7905,43 +7896,43 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C122" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D122" t="s">
         <v>54</v>
       </c>
       <c r="E122" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F122" t="s">
         <v>21</v>
       </c>
       <c r="G122" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="H122" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K122">
-        <v>42.005598999999997</v>
+        <v>41.851723999999997</v>
       </c>
       <c r="L122">
-        <v>-87.782921000000002</v>
+        <v>-87.661697000000004</v>
       </c>
       <c r="M122" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="N122">
-        <v>41.927070499999999</v>
+        <v>41.890661000000001</v>
       </c>
       <c r="O122">
-        <v>-87.641565499999999</v>
+        <v>-87.671790599999994</v>
       </c>
       <c r="P122" t="s">
         <v>32</v>
@@ -7952,40 +7943,43 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C123" t="s">
-        <v>473</v>
+        <v>84</v>
+      </c>
+      <c r="D123" t="s">
+        <v>54</v>
       </c>
       <c r="E123" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F123" t="s">
         <v>21</v>
       </c>
       <c r="G123" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H123" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K123">
-        <v>41.959733999999997</v>
+        <v>41.820988</v>
       </c>
       <c r="L123">
-        <v>-87.768660999999994</v>
+        <v>-87.687297000000001</v>
       </c>
       <c r="M123" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N123">
-        <v>41.886957099999997</v>
+        <v>41.869106500000001</v>
       </c>
       <c r="O123">
-        <v>-87.651906400000001</v>
+        <v>-87.6649156</v>
       </c>
       <c r="P123" t="s">
         <v>32</v>
@@ -7996,43 +7990,43 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C124" t="s">
-        <v>439</v>
+        <v>133</v>
       </c>
       <c r="D124" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E124" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F124" t="s">
         <v>21</v>
       </c>
       <c r="G124" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H124" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K124">
-        <v>41.851723999999997</v>
+        <v>41.984386000000001</v>
       </c>
       <c r="L124">
-        <v>-87.661697000000004</v>
+        <v>-87.767859000000001</v>
       </c>
       <c r="M124" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N124">
-        <v>41.890661000000001</v>
+        <v>41.869595699999998</v>
       </c>
       <c r="O124">
-        <v>-87.671790599999994</v>
+        <v>-87.657438900000002</v>
       </c>
       <c r="P124" t="s">
         <v>32</v>
@@ -8043,46 +8037,46 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C125" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="D125" t="s">
         <v>54</v>
       </c>
       <c r="E125" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F125" t="s">
         <v>21</v>
       </c>
       <c r="G125" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H125" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K125">
-        <v>41.820988</v>
+        <v>41.965045000000003</v>
       </c>
       <c r="L125">
-        <v>-87.687297000000001</v>
+        <v>-87.575958</v>
       </c>
       <c r="M125" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N125">
-        <v>41.869106500000001</v>
+        <v>41.869528199999998</v>
       </c>
       <c r="O125">
-        <v>-87.6649156</v>
+        <v>-87.665284</v>
       </c>
       <c r="P125" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q125" t="s">
         <v>26</v>
@@ -8090,43 +8084,43 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C126" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="D126" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="E126" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F126" t="s">
         <v>21</v>
       </c>
       <c r="G126" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="H126" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K126">
-        <v>41.984386000000001</v>
+        <v>41.921059999999997</v>
       </c>
       <c r="L126">
-        <v>-87.767859000000001</v>
+        <v>-87.731966</v>
       </c>
       <c r="M126" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N126">
-        <v>41.869595699999998</v>
+        <v>41.873277199999997</v>
       </c>
       <c r="O126">
-        <v>-87.657438900000002</v>
+        <v>-87.624588299999999</v>
       </c>
       <c r="P126" t="s">
         <v>32</v>
@@ -8137,46 +8131,46 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C127" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D127" t="s">
         <v>54</v>
       </c>
       <c r="E127" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F127" t="s">
         <v>21</v>
       </c>
       <c r="G127" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H127" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K127">
-        <v>41.965045000000003</v>
+        <v>41.901525999999997</v>
       </c>
       <c r="L127">
-        <v>-87.575958</v>
+        <v>-87.627697999999995</v>
       </c>
       <c r="M127" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N127">
-        <v>41.869528199999998</v>
+        <v>41.896035400000002</v>
       </c>
       <c r="O127">
-        <v>-87.665284</v>
+        <v>-87.651032000000001</v>
       </c>
       <c r="P127" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q127" t="s">
         <v>26</v>
@@ -8184,43 +8178,40 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C128" t="s">
-        <v>28</v>
-      </c>
-      <c r="D128" t="s">
-        <v>54</v>
+        <v>491</v>
       </c>
       <c r="E128" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F128" t="s">
         <v>21</v>
       </c>
       <c r="G128" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="H128" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K128">
-        <v>41.921059999999997</v>
+        <v>41.814283000000003</v>
       </c>
       <c r="L128">
-        <v>-87.731966</v>
+        <v>-87.755898000000002</v>
       </c>
       <c r="M128" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="N128">
-        <v>41.873277199999997</v>
+        <v>41.871405000000003</v>
       </c>
       <c r="O128">
-        <v>-87.624588299999999</v>
+        <v>-88.3057692</v>
       </c>
       <c r="P128" t="s">
         <v>32</v>
@@ -8231,43 +8222,43 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C129" t="s">
-        <v>137</v>
+        <v>435</v>
       </c>
       <c r="D129" t="s">
-        <v>54</v>
+        <v>495</v>
       </c>
       <c r="E129" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F129" t="s">
         <v>21</v>
       </c>
       <c r="G129" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="H129" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="K129">
-        <v>41.901525999999997</v>
+        <v>41.944726000000003</v>
       </c>
       <c r="L129">
-        <v>-87.627697999999995</v>
+        <v>-87.621848</v>
       </c>
       <c r="M129" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="N129">
-        <v>41.896035400000002</v>
+        <v>41.644561299999999</v>
       </c>
       <c r="O129">
-        <v>-87.651032000000001</v>
+        <v>-87.517024500000005</v>
       </c>
       <c r="P129" t="s">
         <v>32</v>
@@ -8278,43 +8269,46 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C130" t="s">
-        <v>495</v>
+        <v>28</v>
+      </c>
+      <c r="D130" t="s">
+        <v>29</v>
       </c>
       <c r="E130" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F130" t="s">
         <v>21</v>
       </c>
       <c r="G130" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="H130" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K130">
-        <v>41.814283000000003</v>
+        <v>41.795954000000002</v>
       </c>
       <c r="L130">
-        <v>-87.755898000000002</v>
+        <v>-87.720765999999998</v>
       </c>
       <c r="M130" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="N130">
-        <v>41.871405000000003</v>
+        <v>41.838874300000001</v>
       </c>
       <c r="O130">
-        <v>-88.3057692</v>
+        <v>-87.909283799999997</v>
       </c>
       <c r="P130" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q130" t="s">
         <v>26</v>
@@ -8322,43 +8316,43 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C131" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
       <c r="D131" t="s">
-        <v>499</v>
+        <v>29</v>
       </c>
       <c r="E131" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F131" t="s">
         <v>21</v>
       </c>
       <c r="G131" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H131" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="K131">
-        <v>41.944726000000003</v>
+        <v>41.977516999999999</v>
       </c>
       <c r="L131">
-        <v>-87.621848</v>
+        <v>-87.702701000000005</v>
       </c>
       <c r="M131" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="N131">
-        <v>41.644561299999999</v>
+        <v>41.9430725</v>
       </c>
       <c r="O131">
-        <v>-87.517024500000005</v>
+        <v>-87.653040300000001</v>
       </c>
       <c r="P131" t="s">
         <v>32</v>
@@ -8369,43 +8363,40 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C132" t="s">
-        <v>28</v>
-      </c>
-      <c r="D132" t="s">
-        <v>29</v>
+        <v>203</v>
       </c>
       <c r="E132" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F132" t="s">
         <v>21</v>
       </c>
       <c r="G132" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H132" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K132">
-        <v>41.795954000000002</v>
+        <v>42.002163000000003</v>
       </c>
       <c r="L132">
-        <v>-87.720765999999998</v>
+        <v>-87.664597999999998</v>
       </c>
       <c r="M132" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="N132">
-        <v>41.838874300000001</v>
+        <v>41.927395799999999</v>
       </c>
       <c r="O132">
-        <v>-87.909283799999997</v>
+        <v>-87.911038099999999</v>
       </c>
       <c r="P132" t="s">
         <v>25</v>
@@ -8416,43 +8407,43 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C133" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D133" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E133" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F133" t="s">
         <v>21</v>
       </c>
       <c r="G133" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="H133" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K133">
-        <v>41.977516999999999</v>
+        <v>41.94415</v>
       </c>
       <c r="L133">
-        <v>-87.702701000000005</v>
+        <v>-87.726804999999999</v>
       </c>
       <c r="M133" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="N133">
-        <v>41.9430725</v>
+        <v>41.894209199999999</v>
       </c>
       <c r="O133">
-        <v>-87.653040300000001</v>
+        <v>-87.632328299999998</v>
       </c>
       <c r="P133" t="s">
         <v>32</v>
@@ -8463,43 +8454,46 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C134" t="s">
-        <v>207</v>
+        <v>28</v>
+      </c>
+      <c r="D134" t="s">
+        <v>54</v>
       </c>
       <c r="E134" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F134" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G134" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H134" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K134">
-        <v>42.002163000000003</v>
+        <v>41.881168000000002</v>
       </c>
       <c r="L134">
-        <v>-87.664597999999998</v>
+        <v>-87.628026000000006</v>
       </c>
       <c r="M134" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="N134">
-        <v>41.927395799999999</v>
+        <v>41.8818883</v>
       </c>
       <c r="O134">
-        <v>-87.911038099999999</v>
+        <v>-87.654976500000004</v>
       </c>
       <c r="P134" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q134" t="s">
         <v>26</v>
@@ -8507,43 +8501,43 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C135" t="s">
-        <v>513</v>
+        <v>221</v>
       </c>
       <c r="D135" t="s">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="E135" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F135" t="s">
         <v>21</v>
       </c>
       <c r="G135" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H135" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K135">
-        <v>41.94415</v>
+        <v>41.975510999999997</v>
       </c>
       <c r="L135">
-        <v>-87.726804999999999</v>
+        <v>-87.588469000000003</v>
       </c>
       <c r="M135" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N135">
-        <v>41.894209199999999</v>
+        <v>41.886594700000003</v>
       </c>
       <c r="O135">
-        <v>-87.632328299999998</v>
+        <v>-87.639574800000005</v>
       </c>
       <c r="P135" t="s">
         <v>32</v>
@@ -8554,43 +8548,43 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C136" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="D136" t="s">
         <v>54</v>
       </c>
       <c r="E136" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F136" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G136" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="H136" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K136">
-        <v>41.881168000000002</v>
+        <v>42.015093999999998</v>
       </c>
       <c r="L136">
-        <v>-87.628026000000006</v>
+        <v>-87.634698</v>
       </c>
       <c r="M136" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N136">
-        <v>41.8818883</v>
+        <v>41.934005399999997</v>
       </c>
       <c r="O136">
-        <v>-87.654976500000004</v>
+        <v>-87.644222999999997</v>
       </c>
       <c r="P136" t="s">
         <v>32</v>
@@ -8601,43 +8595,43 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C137" t="s">
-        <v>225</v>
+        <v>522</v>
       </c>
       <c r="D137" t="s">
-        <v>151</v>
+        <v>523</v>
       </c>
       <c r="E137" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F137" t="s">
         <v>21</v>
       </c>
       <c r="G137" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H137" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="K137">
-        <v>41.975510999999997</v>
+        <v>41.822026999999999</v>
       </c>
       <c r="L137">
-        <v>-87.588469000000003</v>
+        <v>-87.615695000000002</v>
       </c>
       <c r="M137" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="N137">
-        <v>41.886594700000003</v>
+        <v>41.8776571</v>
       </c>
       <c r="O137">
-        <v>-87.639574800000005</v>
+        <v>-87.640669700000004</v>
       </c>
       <c r="P137" t="s">
         <v>32</v>
@@ -8648,43 +8642,43 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A138">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C138" t="s">
-        <v>137</v>
+        <v>527</v>
       </c>
       <c r="D138" t="s">
-        <v>54</v>
+        <v>414</v>
       </c>
       <c r="E138" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F138" t="s">
         <v>21</v>
       </c>
       <c r="G138" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="H138" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K138">
-        <v>42.015093999999998</v>
+        <v>41.813372000000001</v>
       </c>
       <c r="L138">
-        <v>-87.634698</v>
+        <v>-87.681759</v>
       </c>
       <c r="M138" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="N138">
-        <v>41.934005399999997</v>
+        <v>41.885708100000002</v>
       </c>
       <c r="O138">
-        <v>-87.644222999999997</v>
+        <v>-87.651759200000001</v>
       </c>
       <c r="P138" t="s">
         <v>32</v>
@@ -8695,43 +8689,43 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A139">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C139" t="s">
-        <v>526</v>
+        <v>133</v>
       </c>
       <c r="D139" t="s">
-        <v>527</v>
+        <v>29</v>
       </c>
       <c r="E139" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F139" t="s">
         <v>21</v>
       </c>
       <c r="G139" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="H139" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K139">
-        <v>41.822026999999999</v>
+        <v>41.802788999999997</v>
       </c>
       <c r="L139">
-        <v>-87.615695000000002</v>
+        <v>-87.605687000000003</v>
       </c>
       <c r="M139" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="N139">
-        <v>41.8776571</v>
+        <v>41.885001099999997</v>
       </c>
       <c r="O139">
-        <v>-87.640669700000004</v>
+        <v>-87.652478400000007</v>
       </c>
       <c r="P139" t="s">
         <v>32</v>
@@ -8742,46 +8736,46 @@
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A140">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C140" t="s">
-        <v>531</v>
+        <v>428</v>
       </c>
       <c r="D140" t="s">
-        <v>418</v>
+        <v>29</v>
       </c>
       <c r="E140" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F140" t="s">
         <v>21</v>
       </c>
       <c r="G140" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H140" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K140">
-        <v>41.813372000000001</v>
+        <v>41.847679999999997</v>
       </c>
       <c r="L140">
-        <v>-87.681759</v>
+        <v>-87.801886999999994</v>
       </c>
       <c r="M140" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N140">
-        <v>41.885708100000002</v>
+        <v>41.930154299999998</v>
       </c>
       <c r="O140">
-        <v>-87.651759200000001</v>
+        <v>-87.735514800000004</v>
       </c>
       <c r="P140" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q140" t="s">
         <v>26</v>
@@ -8789,43 +8783,43 @@
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A141">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C141" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="D141" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E141" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F141" t="s">
         <v>21</v>
       </c>
       <c r="G141" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H141" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="K141">
-        <v>41.802788999999997</v>
+        <v>41.796999999999997</v>
       </c>
       <c r="L141">
-        <v>-87.605687000000003</v>
+        <v>-87.820357999999999</v>
       </c>
       <c r="M141" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N141">
-        <v>41.885001099999997</v>
+        <v>41.884944500000003</v>
       </c>
       <c r="O141">
-        <v>-87.652478400000007</v>
+        <v>-87.650803800000006</v>
       </c>
       <c r="P141" t="s">
         <v>32</v>
@@ -8836,46 +8830,46 @@
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A142">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C142" t="s">
-        <v>432</v>
+        <v>77</v>
       </c>
       <c r="D142" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="E142" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F142" t="s">
         <v>21</v>
       </c>
       <c r="G142" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H142" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K142">
-        <v>41.847679999999997</v>
+        <v>41.867626999999999</v>
       </c>
       <c r="L142">
-        <v>-87.801886999999994</v>
+        <v>-87.728584999999995</v>
       </c>
       <c r="M142" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N142">
-        <v>41.930154299999998</v>
+        <v>41.869524200000001</v>
       </c>
       <c r="O142">
-        <v>-87.735514800000004</v>
+        <v>-87.662709100000001</v>
       </c>
       <c r="P142" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q142" t="s">
         <v>26</v>
@@ -8883,43 +8877,43 @@
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A143">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C143" t="s">
-        <v>247</v>
+        <v>543</v>
       </c>
       <c r="D143" t="s">
         <v>45</v>
       </c>
       <c r="E143" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F143" t="s">
         <v>21</v>
       </c>
       <c r="G143" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="H143" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K143">
-        <v>41.796999999999997</v>
+        <v>41.931722999999998</v>
       </c>
       <c r="L143">
-        <v>-87.820357999999999</v>
+        <v>-87.569728999999995</v>
       </c>
       <c r="M143" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N143">
-        <v>41.884944500000003</v>
+        <v>41.6669816</v>
       </c>
       <c r="O143">
-        <v>-87.650803800000006</v>
+        <v>-87.7961229</v>
       </c>
       <c r="P143" t="s">
         <v>32</v>
@@ -8930,43 +8924,40 @@
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A144">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C144" t="s">
-        <v>77</v>
-      </c>
-      <c r="D144" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="E144" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F144" t="s">
         <v>21</v>
       </c>
       <c r="G144" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H144" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K144">
-        <v>41.867626999999999</v>
+        <v>41.838185000000003</v>
       </c>
       <c r="L144">
-        <v>-87.728584999999995</v>
+        <v>-87.627647999999994</v>
       </c>
       <c r="M144" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="N144">
-        <v>41.869524200000001</v>
+        <v>41.699577300000001</v>
       </c>
       <c r="O144">
-        <v>-87.662709100000001</v>
+        <v>-87.796981799999998</v>
       </c>
       <c r="P144" t="s">
         <v>32</v>
@@ -8977,43 +8968,43 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A145">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C145" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D145" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E145" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F145" t="s">
         <v>21</v>
       </c>
       <c r="G145" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="H145" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K145">
-        <v>41.931722999999998</v>
+        <v>41.883918000000001</v>
       </c>
       <c r="L145">
-        <v>-87.569728999999995</v>
+        <v>-87.620608000000004</v>
       </c>
       <c r="M145" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="N145">
-        <v>41.6669816</v>
+        <v>41.895682200000003</v>
       </c>
       <c r="O145">
-        <v>-87.7961229</v>
+        <v>-87.654796300000001</v>
       </c>
       <c r="P145" t="s">
         <v>32</v>
@@ -9024,40 +9015,43 @@
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A146">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C146" t="s">
-        <v>112</v>
+        <v>435</v>
+      </c>
+      <c r="D146" t="s">
+        <v>54</v>
       </c>
       <c r="E146" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F146" t="s">
         <v>21</v>
       </c>
       <c r="G146" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H146" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K146">
-        <v>41.838185000000003</v>
+        <v>41.895102000000001</v>
       </c>
       <c r="L146">
-        <v>-87.627647999999994</v>
+        <v>-87.554062000000002</v>
       </c>
       <c r="M146" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="N146">
-        <v>41.699577300000001</v>
+        <v>41.886268399999999</v>
       </c>
       <c r="O146">
-        <v>-87.796981799999998</v>
+        <v>-87.650208599999999</v>
       </c>
       <c r="P146" t="s">
         <v>32</v>
@@ -9068,43 +9062,43 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A147">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C147" t="s">
-        <v>554</v>
+        <v>77</v>
       </c>
       <c r="D147" t="s">
-        <v>54</v>
+        <v>147</v>
       </c>
       <c r="E147" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F147" t="s">
         <v>21</v>
       </c>
       <c r="G147" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H147" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K147">
-        <v>41.883918000000001</v>
+        <v>41.896523000000002</v>
       </c>
       <c r="L147">
-        <v>-87.620608000000004</v>
+        <v>-87.694542999999996</v>
       </c>
       <c r="M147" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N147">
-        <v>41.895682200000003</v>
+        <v>41.885885999999999</v>
       </c>
       <c r="O147">
-        <v>-87.654796300000001</v>
+        <v>-87.648449999999997</v>
       </c>
       <c r="P147" t="s">
         <v>32</v>
@@ -9115,43 +9109,43 @@
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A148">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C148" t="s">
-        <v>439</v>
+        <v>560</v>
       </c>
       <c r="D148" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E148" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F148" t="s">
         <v>21</v>
       </c>
       <c r="G148" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="H148" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K148">
-        <v>41.895102000000001</v>
+        <v>41.906731999999998</v>
       </c>
       <c r="L148">
-        <v>-87.554062000000002</v>
+        <v>-87.808695</v>
       </c>
       <c r="M148" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="N148">
-        <v>41.886268399999999</v>
+        <v>41.895980799999997</v>
       </c>
       <c r="O148">
-        <v>-87.650208599999999</v>
+        <v>-87.653102399999995</v>
       </c>
       <c r="P148" t="s">
         <v>32</v>
@@ -9162,46 +9156,46 @@
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A149">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C149" t="s">
-        <v>77</v>
+        <v>564</v>
       </c>
       <c r="D149" t="s">
-        <v>151</v>
+        <v>45</v>
       </c>
       <c r="E149" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F149" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G149" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="H149" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="K149">
-        <v>41.896523000000002</v>
+        <v>41.855462000000003</v>
       </c>
       <c r="L149">
-        <v>-87.694542999999996</v>
+        <v>-87.632435999999998</v>
       </c>
       <c r="M149" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="N149">
-        <v>41.885885999999999</v>
+        <v>41.846158199999998</v>
       </c>
       <c r="O149">
-        <v>-87.648449999999997</v>
+        <v>-87.646274899999995</v>
       </c>
       <c r="P149" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q149" t="s">
         <v>26</v>
@@ -9209,43 +9203,43 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A150">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C150" t="s">
-        <v>564</v>
+        <v>435</v>
       </c>
       <c r="D150" t="s">
         <v>29</v>
       </c>
       <c r="E150" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F150" t="s">
         <v>21</v>
       </c>
       <c r="G150" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="H150" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K150">
-        <v>41.906731999999998</v>
+        <v>41.938696</v>
       </c>
       <c r="L150">
-        <v>-87.808695</v>
+        <v>-87.616358000000005</v>
       </c>
       <c r="M150" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="N150">
-        <v>41.895980799999997</v>
+        <v>41.8691897</v>
       </c>
       <c r="O150">
-        <v>-87.653102399999995</v>
+        <v>-87.660693699999996</v>
       </c>
       <c r="P150" t="s">
         <v>32</v>
@@ -9256,46 +9250,46 @@
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A151">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C151" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D151" t="s">
         <v>45</v>
       </c>
       <c r="E151" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F151" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G151" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H151" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K151">
-        <v>41.855462000000003</v>
+        <v>41.926262000000001</v>
       </c>
       <c r="L151">
-        <v>-87.632435999999998</v>
+        <v>-87.792100000000005</v>
       </c>
       <c r="M151" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N151">
-        <v>41.846158199999998</v>
+        <v>41.882434699999997</v>
       </c>
       <c r="O151">
-        <v>-87.646274899999995</v>
+        <v>-87.641370600000002</v>
       </c>
       <c r="P151" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q151" t="s">
         <v>26</v>
@@ -9303,43 +9297,43 @@
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A152">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C152" t="s">
-        <v>439</v>
+        <v>575</v>
       </c>
       <c r="D152" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E152" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F152" t="s">
         <v>21</v>
       </c>
       <c r="G152" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="H152" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K152">
-        <v>41.938696</v>
+        <v>41.926631999999998</v>
       </c>
       <c r="L152">
-        <v>-87.616358000000005</v>
+        <v>-87.603604000000004</v>
       </c>
       <c r="M152" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N152">
-        <v>41.8691897</v>
+        <v>41.877078699999998</v>
       </c>
       <c r="O152">
-        <v>-87.660693699999996</v>
+        <v>-87.627206400000006</v>
       </c>
       <c r="P152" t="s">
         <v>32</v>
@@ -9350,43 +9344,43 @@
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A153">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C153" t="s">
-        <v>575</v>
+        <v>28</v>
       </c>
       <c r="D153" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E153" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F153" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G153" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H153" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="K153">
-        <v>41.926262000000001</v>
+        <v>41.877988999999999</v>
       </c>
       <c r="L153">
-        <v>-87.792100000000005</v>
+        <v>-87.621838999999994</v>
       </c>
       <c r="M153" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="N153">
-        <v>41.882434699999997</v>
+        <v>41.909773299999998</v>
       </c>
       <c r="O153">
-        <v>-87.641370600000002</v>
+        <v>-87.676802300000006</v>
       </c>
       <c r="P153" t="s">
         <v>32</v>
@@ -9397,43 +9391,43 @@
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A154">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C154" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D154" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E154" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F154" t="s">
         <v>21</v>
       </c>
       <c r="G154" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H154" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="K154">
-        <v>41.926631999999998</v>
+        <v>41.777489000000003</v>
       </c>
       <c r="L154">
-        <v>-87.603604000000004</v>
+        <v>-87.590727000000001</v>
       </c>
       <c r="M154" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="N154">
-        <v>41.877078699999998</v>
+        <v>41.883352000000002</v>
       </c>
       <c r="O154">
-        <v>-87.627206400000006</v>
+        <v>-87.637215600000005</v>
       </c>
       <c r="P154" t="s">
         <v>32</v>
@@ -9444,43 +9438,43 @@
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A155">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B155" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C155" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D155" t="s">
         <v>54</v>
       </c>
       <c r="E155" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F155" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G155" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H155" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="K155">
-        <v>41.877988999999999</v>
+        <v>41.824922999999998</v>
       </c>
       <c r="L155">
-        <v>-87.621838999999994</v>
+        <v>-87.614103999999998</v>
       </c>
       <c r="M155" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="N155">
-        <v>41.909773299999998</v>
+        <v>41.880393300000001</v>
       </c>
       <c r="O155">
-        <v>-87.676802300000006</v>
+        <v>-87.640124400000005</v>
       </c>
       <c r="P155" t="s">
         <v>32</v>
@@ -9491,43 +9485,43 @@
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A156">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B156" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C156" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D156" t="s">
         <v>54</v>
       </c>
       <c r="E156" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F156" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G156" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="H156" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="K156">
-        <v>41.777489000000003</v>
+        <v>41.880077</v>
       </c>
       <c r="L156">
-        <v>-87.590727000000001</v>
+        <v>-87.630983000000001</v>
       </c>
       <c r="M156" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="N156">
-        <v>41.883352000000002</v>
+        <v>41.884088900000002</v>
       </c>
       <c r="O156">
-        <v>-87.637215600000005</v>
+        <v>-87.640855599999995</v>
       </c>
       <c r="P156" t="s">
         <v>32</v>
@@ -9538,43 +9532,43 @@
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A157">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B157" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C157" t="s">
-        <v>18</v>
+        <v>593</v>
       </c>
       <c r="D157" t="s">
-        <v>54</v>
+        <v>594</v>
       </c>
       <c r="E157" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F157" t="s">
         <v>21</v>
       </c>
       <c r="G157" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="H157" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="K157">
-        <v>41.824922999999998</v>
+        <v>41.888505000000002</v>
       </c>
       <c r="L157">
-        <v>-87.614103999999998</v>
+        <v>-87.678332999999995</v>
       </c>
       <c r="M157" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="N157">
-        <v>41.880393300000001</v>
+        <v>41.854724699999998</v>
       </c>
       <c r="O157">
-        <v>-87.640124400000005</v>
+        <v>-87.6325267</v>
       </c>
       <c r="P157" t="s">
         <v>32</v>
@@ -9585,43 +9579,43 @@
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A158">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B158" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C158" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D158" t="s">
         <v>54</v>
       </c>
       <c r="E158" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F158" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G158" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="H158" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="K158">
-        <v>41.880077</v>
+        <v>41.953377000000003</v>
       </c>
       <c r="L158">
-        <v>-87.630983000000001</v>
+        <v>-87.765978000000004</v>
       </c>
       <c r="M158" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N158">
-        <v>41.884088900000002</v>
+        <v>41.879829999999998</v>
       </c>
       <c r="O158">
-        <v>-87.640855599999995</v>
+        <v>-87.630533499999999</v>
       </c>
       <c r="P158" t="s">
         <v>32</v>
@@ -9632,46 +9626,46 @@
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A159">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B159" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C159" t="s">
-        <v>597</v>
+        <v>28</v>
       </c>
       <c r="D159" t="s">
-        <v>598</v>
+        <v>54</v>
       </c>
       <c r="E159" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F159" t="s">
         <v>21</v>
       </c>
       <c r="G159" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H159" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K159">
-        <v>41.888505000000002</v>
+        <v>41.876989999999999</v>
       </c>
       <c r="L159">
-        <v>-87.678332999999995</v>
+        <v>-87.716179999999994</v>
       </c>
       <c r="M159" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="N159">
-        <v>41.854724699999998</v>
+        <v>41.838874300000001</v>
       </c>
       <c r="O159">
-        <v>-87.6325267</v>
+        <v>-87.909283799999997</v>
       </c>
       <c r="P159" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q159" t="s">
         <v>26</v>
@@ -9679,43 +9673,43 @@
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A160">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B160" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C160" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="D160" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E160" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F160" t="s">
         <v>21</v>
       </c>
       <c r="G160" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="H160" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="K160">
-        <v>41.953377000000003</v>
+        <v>41.953209999999999</v>
       </c>
       <c r="L160">
-        <v>-87.765978000000004</v>
+        <v>-87.641233</v>
       </c>
       <c r="M160" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="N160">
-        <v>41.879829999999998</v>
+        <v>41.953753499999998</v>
       </c>
       <c r="O160">
-        <v>-87.630533499999999</v>
+        <v>-87.702103300000005</v>
       </c>
       <c r="P160" t="s">
         <v>32</v>
@@ -9726,46 +9720,46 @@
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A161">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B161" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C161" t="s">
-        <v>28</v>
+        <v>608</v>
       </c>
       <c r="D161" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E161" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F161" t="s">
         <v>21</v>
       </c>
       <c r="G161" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="H161" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="K161">
-        <v>41.876989999999999</v>
+        <v>41.902208000000002</v>
       </c>
       <c r="L161">
-        <v>-87.716179999999994</v>
+        <v>-87.853800000000007</v>
       </c>
       <c r="M161" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="N161">
-        <v>41.838874300000001</v>
+        <v>41.966780499999999</v>
       </c>
       <c r="O161">
-        <v>-87.909283799999997</v>
+        <v>-87.713773900000007</v>
       </c>
       <c r="P161" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q161" t="s">
         <v>26</v>
@@ -9773,46 +9767,43 @@
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A162">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B162" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C162" t="s">
-        <v>608</v>
-      </c>
-      <c r="D162" t="s">
-        <v>45</v>
+        <v>612</v>
       </c>
       <c r="E162" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F162" t="s">
         <v>21</v>
       </c>
       <c r="G162" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="H162" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="K162">
-        <v>41.953209999999999</v>
+        <v>42.024825999999997</v>
       </c>
       <c r="L162">
-        <v>-87.641233</v>
+        <v>-87.800807000000006</v>
       </c>
       <c r="M162" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="N162">
-        <v>41.953753499999998</v>
+        <v>41.8807945</v>
       </c>
       <c r="O162">
-        <v>-87.702103300000005</v>
+        <v>-87.723842899999994</v>
       </c>
       <c r="P162" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q162" t="s">
         <v>26</v>
@@ -9820,43 +9811,40 @@
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A163">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B163" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C163" t="s">
-        <v>612</v>
-      </c>
-      <c r="D163" t="s">
-        <v>45</v>
+        <v>616</v>
       </c>
       <c r="E163" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F163" t="s">
         <v>21</v>
       </c>
       <c r="G163" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="H163" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="K163">
-        <v>41.902208000000002</v>
+        <v>41.916356999999998</v>
       </c>
       <c r="L163">
-        <v>-87.853800000000007</v>
+        <v>-87.703245999999993</v>
       </c>
       <c r="M163" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="N163">
-        <v>41.966780499999999</v>
+        <v>42.044701400000001</v>
       </c>
       <c r="O163">
-        <v>-87.713773900000007</v>
+        <v>-87.980540700000006</v>
       </c>
       <c r="P163" t="s">
         <v>32</v>
@@ -9867,43 +9855,46 @@
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A164">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B164" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C164" t="s">
-        <v>616</v>
+        <v>360</v>
+      </c>
+      <c r="D164" t="s">
+        <v>620</v>
       </c>
       <c r="E164" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F164" t="s">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="G164" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="H164" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K164">
-        <v>42.024825999999997</v>
+        <v>41.973100000000002</v>
       </c>
       <c r="L164">
-        <v>-87.800807000000006</v>
+        <v>-87.655199999999994</v>
       </c>
       <c r="M164" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="N164">
-        <v>41.8807945</v>
+        <v>41.973407999999999</v>
       </c>
       <c r="O164">
-        <v>-87.723842899999994</v>
+        <v>-87.656086599999995</v>
       </c>
       <c r="P164" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q164" t="s">
         <v>26</v>
@@ -9911,40 +9902,43 @@
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A165">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B165" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C165" t="s">
-        <v>620</v>
+        <v>624</v>
+      </c>
+      <c r="D165" t="s">
+        <v>45</v>
       </c>
       <c r="E165" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F165" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G165" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="H165" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="K165">
-        <v>41.916356999999998</v>
+        <v>41.899777</v>
       </c>
       <c r="L165">
-        <v>-87.703245999999993</v>
+        <v>-87.649994000000007</v>
       </c>
       <c r="M165" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="N165">
-        <v>42.044701400000001</v>
+        <v>41.838688900000001</v>
       </c>
       <c r="O165">
-        <v>-87.980540700000006</v>
+        <v>-87.646587299999993</v>
       </c>
       <c r="P165" t="s">
         <v>32</v>
@@ -9955,43 +9949,40 @@
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A166">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B166" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C166" t="s">
-        <v>364</v>
-      </c>
-      <c r="D166" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E166" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F166" t="s">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="G166" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="H166" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K166">
-        <v>41.973100000000002</v>
+        <v>41.834268000000002</v>
       </c>
       <c r="L166">
-        <v>-87.655199999999994</v>
+        <v>-87.527253000000002</v>
       </c>
       <c r="M166" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="N166">
-        <v>41.973407999999999</v>
+        <v>41.941344000000001</v>
       </c>
       <c r="O166">
-        <v>-87.656086599999995</v>
+        <v>-87.644217299999994</v>
       </c>
       <c r="P166" t="s">
         <v>32</v>
@@ -10002,43 +9993,43 @@
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A167">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B167" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C167" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D167" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E167" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F167" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G167" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="H167" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="K167">
-        <v>41.899777</v>
+        <v>41.9529</v>
       </c>
       <c r="L167">
-        <v>-87.649994000000007</v>
+        <v>-87.627502000000007</v>
       </c>
       <c r="M167" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="N167">
-        <v>41.838688900000001</v>
+        <v>41.968218999999998</v>
       </c>
       <c r="O167">
-        <v>-87.646587299999993</v>
+        <v>-87.715681900000007</v>
       </c>
       <c r="P167" t="s">
         <v>32</v>
@@ -10049,40 +10040,43 @@
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A168">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B168" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C168" t="s">
-        <v>632</v>
+        <v>636</v>
+      </c>
+      <c r="D168" t="s">
+        <v>45</v>
       </c>
       <c r="E168" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F168" t="s">
         <v>21</v>
       </c>
       <c r="G168" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="H168" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="K168">
-        <v>41.834268000000002</v>
+        <v>41.891233999999997</v>
       </c>
       <c r="L168">
-        <v>-87.527253000000002</v>
+        <v>-87.586796000000007</v>
       </c>
       <c r="M168" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="N168">
-        <v>41.941344000000001</v>
+        <v>41.836016299999997</v>
       </c>
       <c r="O168">
-        <v>-87.644217299999994</v>
+        <v>-87.645831799999996</v>
       </c>
       <c r="P168" t="s">
         <v>32</v>
@@ -10093,142 +10087,48 @@
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A169">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B169" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C169" t="s">
-        <v>636</v>
+        <v>435</v>
       </c>
       <c r="D169" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E169" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F169" t="s">
         <v>21</v>
       </c>
       <c r="G169" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="H169" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K169">
-        <v>41.9529</v>
+        <v>41.864972999999999</v>
       </c>
       <c r="L169">
-        <v>-87.627502000000007</v>
+        <v>-87.686687000000006</v>
       </c>
       <c r="M169" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="N169">
-        <v>41.968218999999998</v>
+        <v>41.867675499999997</v>
       </c>
       <c r="O169">
-        <v>-87.715681900000007</v>
+        <v>-87.626062700000006</v>
       </c>
       <c r="P169" t="s">
         <v>32</v>
       </c>
       <c r="Q169" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A170">
-        <v>169</v>
-      </c>
-      <c r="B170" t="s">
-        <v>639</v>
-      </c>
-      <c r="C170" t="s">
-        <v>640</v>
-      </c>
-      <c r="D170" t="s">
-        <v>45</v>
-      </c>
-      <c r="E170" t="s">
-        <v>414</v>
-      </c>
-      <c r="F170" t="s">
-        <v>21</v>
-      </c>
-      <c r="G170" t="s">
-        <v>641</v>
-      </c>
-      <c r="H170" t="s">
-        <v>641</v>
-      </c>
-      <c r="K170">
-        <v>41.891233999999997</v>
-      </c>
-      <c r="L170">
-        <v>-87.586796000000007</v>
-      </c>
-      <c r="M170" t="s">
-        <v>642</v>
-      </c>
-      <c r="N170">
-        <v>41.836016299999997</v>
-      </c>
-      <c r="O170">
-        <v>-87.645831799999996</v>
-      </c>
-      <c r="P170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q170" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A171">
-        <v>170</v>
-      </c>
-      <c r="B171" t="s">
-        <v>643</v>
-      </c>
-      <c r="C171" t="s">
-        <v>439</v>
-      </c>
-      <c r="D171" t="s">
-        <v>54</v>
-      </c>
-      <c r="E171" t="s">
-        <v>414</v>
-      </c>
-      <c r="F171" t="s">
-        <v>21</v>
-      </c>
-      <c r="G171" t="s">
-        <v>644</v>
-      </c>
-      <c r="H171" t="s">
-        <v>644</v>
-      </c>
-      <c r="K171">
-        <v>41.864972999999999</v>
-      </c>
-      <c r="L171">
-        <v>-87.686687000000006</v>
-      </c>
-      <c r="M171" t="s">
-        <v>645</v>
-      </c>
-      <c r="N171">
-        <v>41.867675499999997</v>
-      </c>
-      <c r="O171">
-        <v>-87.626062700000006</v>
-      </c>
-      <c r="P171" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q171" t="s">
         <v>26</v>
       </c>
     </row>

--- a/data/food_loc_exact.xlsx
+++ b/data/food_loc_exact.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\food_proj\food_recommendations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB37045-A97F-4C6A-A567-11C73A889744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{827B3459-FDEC-46B5-BEBB-535658F74E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/food_loc_exact.xlsx
+++ b/data/food_loc_exact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\food_proj\food_recommendations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{827B3459-FDEC-46B5-BEBB-535658F74E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CE864E-61A1-4279-AAFA-1C6B8E30F5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3260,10 +3260,10 @@
         <v>110</v>
       </c>
       <c r="N21">
-        <v>38.891522000000002</v>
+        <v>38.9053009</v>
       </c>
       <c r="O21">
-        <v>-77.064962199999997</v>
+        <v>-77.065788100000006</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
